--- a/WP-2/Data_cleaning/ADNI_variables_cleaned2.xlsx
+++ b/WP-2/Data_cleaning/ADNI_variables_cleaned2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/chiara_pollicini_ifabfoundation_org/Documents/Documenti/Github/AIND/WP-2/Data_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_348505CD5357520F62355476585DCE3A8745F34F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF8F6380-572D-454A-9DA3-CA8A1BFA3C02}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_26B1E901577FF60F62355476585DCE3A8745FCA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E61BBE60-48F1-479E-9C64-AD97D5F3A772}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-3705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="316">
   <si>
     <t>file_name</t>
   </si>
@@ -85,9 +85,15 @@
     <t>011_S_0002, 011_S_0003, 022_S_0004, 011_S_0005, 100_S_0006</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>ADNI4</t>
   </si>
   <si>
+    <t>keep</t>
+  </si>
+  <si>
     <t>RID</t>
   </si>
   <si>
@@ -760,18 +766,12 @@
     <t>UCSFFSX51</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>5296.0, 21.0</t>
   </si>
   <si>
     <t>ADNI1, ADNI3, ADNI4</t>
   </si>
   <si>
-    <t>False</t>
-  </si>
-  <si>
     <t>ADNIGO, ADNI2, nv</t>
   </si>
   <si>
@@ -890,6 +890,9 @@
   </si>
   <si>
     <t>11447.0, 6383.0</t>
+  </si>
+  <si>
+    <t>drop</t>
   </si>
   <si>
     <t>4381.7, 2300.1</t>
@@ -983,6 +986,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1403,6 +1407,9 @@
       <c r="H2" t="s">
         <v>20</v>
       </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
       <c r="J2">
         <v>11135</v>
       </c>
@@ -1410,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -1427,16 +1434,19 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3">
         <v>11135</v>
@@ -1445,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -1459,19 +1469,22 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
       </c>
       <c r="J4">
         <v>11135</v>
@@ -1480,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -1494,19 +1507,22 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
       </c>
       <c r="J5">
         <v>11135</v>
@@ -1515,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -1529,19 +1545,22 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J6">
         <v>11129</v>
@@ -1550,13 +1569,13 @@
         <v>6</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -1567,19 +1586,22 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <v>11135</v>
@@ -1588,13 +1610,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -1605,22 +1627,22 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J8">
         <v>10990</v>
@@ -1629,16 +1651,13 @@
         <v>145</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>45</v>
-      </c>
-      <c r="O8" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1649,19 +1668,22 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J9">
         <v>10986</v>
@@ -1670,16 +1692,16 @@
         <v>149</v>
       </c>
       <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>23</v>
       </c>
       <c r="N9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -1690,19 +1712,22 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J10">
         <v>11036</v>
@@ -1711,16 +1736,16 @@
         <v>99</v>
       </c>
       <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1731,19 +1756,22 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J11">
         <v>10937</v>
@@ -1752,16 +1780,16 @@
         <v>198</v>
       </c>
       <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
+        <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1772,19 +1800,22 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J12">
         <v>11067</v>
@@ -1793,16 +1824,16 @@
         <v>68</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -1813,19 +1844,22 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
       </c>
       <c r="I13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J13">
         <v>10951</v>
@@ -1834,16 +1868,16 @@
         <v>184</v>
       </c>
       <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1854,19 +1888,22 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J14">
         <v>10975</v>
@@ -1875,16 +1912,16 @@
         <v>160</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
+        <v>23</v>
       </c>
       <c r="N14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -1895,19 +1932,22 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
       </c>
       <c r="I15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J15">
         <v>8458</v>
@@ -1916,16 +1956,16 @@
         <v>2677</v>
       </c>
       <c r="L15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M15" t="s">
+        <v>23</v>
       </c>
       <c r="N15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1936,19 +1976,22 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
       </c>
       <c r="I16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J16">
         <v>7874</v>
@@ -1957,16 +2000,16 @@
         <v>3261</v>
       </c>
       <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M16" t="s">
+        <v>23</v>
       </c>
       <c r="N16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -1977,19 +2020,22 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
       </c>
       <c r="I17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J17">
         <v>7488</v>
@@ -1998,16 +2044,16 @@
         <v>3647</v>
       </c>
       <c r="L17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M17" t="s">
+        <v>23</v>
       </c>
       <c r="N17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -2018,19 +2064,22 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
       </c>
       <c r="I18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J18">
         <v>7488</v>
@@ -2039,16 +2088,16 @@
         <v>3647</v>
       </c>
       <c r="L18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M18" t="s">
+        <v>23</v>
       </c>
       <c r="N18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -2059,19 +2108,22 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
       </c>
       <c r="I19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J19">
         <v>7488</v>
@@ -2080,13 +2132,13 @@
         <v>3647</v>
       </c>
       <c r="L19" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M19" t="s">
+        <v>23</v>
       </c>
       <c r="O19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -2097,19 +2149,22 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H20" t="s">
+        <v>21</v>
       </c>
       <c r="I20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J20">
         <v>9023</v>
@@ -2118,10 +2173,10 @@
         <v>2112</v>
       </c>
       <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -2132,19 +2187,22 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
       </c>
       <c r="I21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J21">
         <v>11129</v>
@@ -2153,10 +2211,10 @@
         <v>6</v>
       </c>
       <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M21" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -2167,19 +2225,22 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J22">
         <v>11135</v>
@@ -2188,10 +2249,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -2202,19 +2263,22 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
       </c>
       <c r="J23">
         <v>11135</v>
@@ -2223,13 +2287,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M23" t="s">
+        <v>23</v>
       </c>
       <c r="N23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -2240,19 +2304,22 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" t="s">
         <v>86</v>
       </c>
-      <c r="G24" t="s">
-        <v>84</v>
-      </c>
       <c r="H24" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
       </c>
       <c r="J24">
         <v>11135</v>
@@ -2261,13 +2328,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M24" t="s">
+        <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -2278,19 +2345,22 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
       </c>
       <c r="J25">
         <v>11135</v>
@@ -2299,13 +2369,13 @@
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M25" t="s">
+        <v>23</v>
       </c>
       <c r="N25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -2316,19 +2386,22 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s">
         <v>89</v>
       </c>
-      <c r="E26" t="s">
-        <v>91</v>
-      </c>
-      <c r="G26" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" t="s">
-        <v>87</v>
+      <c r="I26" t="s">
+        <v>21</v>
       </c>
       <c r="J26">
         <v>11135</v>
@@ -2337,13 +2410,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M26" t="s">
+        <v>23</v>
       </c>
       <c r="N26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
@@ -2354,19 +2427,22 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
       </c>
       <c r="J27">
         <v>11135</v>
@@ -2375,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M27" t="s">
+        <v>23</v>
       </c>
       <c r="N27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -2392,19 +2468,22 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I28" t="s">
+        <v>21</v>
       </c>
       <c r="J28">
         <v>11135</v>
@@ -2413,13 +2492,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M28" t="s">
+        <v>23</v>
       </c>
       <c r="N28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -2430,19 +2509,22 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
       </c>
       <c r="J29">
         <v>11135</v>
@@ -2451,13 +2533,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M29" t="s">
+        <v>23</v>
       </c>
       <c r="N29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -2468,19 +2550,22 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
       </c>
       <c r="J30">
         <v>11135</v>
@@ -2489,13 +2574,13 @@
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M30" t="s">
+        <v>23</v>
       </c>
       <c r="N30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -2506,19 +2591,22 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G31" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
       </c>
       <c r="J31">
         <v>11135</v>
@@ -2527,13 +2615,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M31" t="s">
+        <v>23</v>
       </c>
       <c r="N31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -2544,19 +2632,22 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
       </c>
       <c r="J32">
         <v>11135</v>
@@ -2565,13 +2656,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M32" t="s">
+        <v>23</v>
       </c>
       <c r="N32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
@@ -2582,19 +2673,22 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
       </c>
       <c r="J33">
         <v>11135</v>
@@ -2603,13 +2697,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M33" t="s">
+        <v>23</v>
       </c>
       <c r="N33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
@@ -2620,19 +2714,22 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
       </c>
       <c r="J34">
         <v>11135</v>
@@ -2641,13 +2738,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M34" t="s">
+        <v>23</v>
       </c>
       <c r="N34" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
@@ -2658,19 +2755,22 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E35" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
       </c>
       <c r="J35">
         <v>11135</v>
@@ -2679,13 +2779,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M35" t="s">
+        <v>23</v>
       </c>
       <c r="N35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -2696,19 +2796,22 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E36" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
       </c>
       <c r="J36">
         <v>11135</v>
@@ -2717,10 +2820,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M36" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
@@ -2731,19 +2834,22 @@
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G37" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
       </c>
       <c r="J37">
         <v>11135</v>
@@ -2752,10 +2858,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M37" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -2766,19 +2872,22 @@
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E38" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
       </c>
       <c r="J38">
         <v>11135</v>
@@ -2787,18 +2896,18 @@
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="M38" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
@@ -2813,7 +2922,10 @@
         <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
       </c>
       <c r="J39">
         <v>1245</v>
@@ -2822,33 +2934,36 @@
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>112</v>
-      </c>
-      <c r="M39" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M39" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H40" t="s">
+        <v>21</v>
       </c>
       <c r="I40" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J40">
         <v>1245</v>
@@ -2857,33 +2972,36 @@
         <v>0</v>
       </c>
       <c r="L40" t="s">
-        <v>112</v>
-      </c>
-      <c r="M40" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M40" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G41" t="s">
         <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>115</v>
+        <v>117</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
       </c>
       <c r="J41">
         <v>1245</v>
@@ -2892,33 +3010,36 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>112</v>
-      </c>
-      <c r="M41" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M41" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G42" t="s">
         <v>19</v>
       </c>
       <c r="H42" t="s">
-        <v>117</v>
+        <v>119</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
       </c>
       <c r="J42">
         <v>1245</v>
@@ -2927,33 +3048,36 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>112</v>
-      </c>
-      <c r="M42" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M42" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D43" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E43" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H43" t="s">
+        <v>21</v>
       </c>
       <c r="I43" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J43">
         <v>1245</v>
@@ -2962,36 +3086,39 @@
         <v>0</v>
       </c>
       <c r="L43" t="s">
-        <v>112</v>
-      </c>
-      <c r="M43" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M43" t="s">
+        <v>23</v>
       </c>
       <c r="N43" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E44" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G44" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H44" t="s">
+        <v>21</v>
       </c>
       <c r="I44" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J44">
         <v>1212</v>
@@ -3000,39 +3127,42 @@
         <v>33</v>
       </c>
       <c r="L44" t="s">
-        <v>112</v>
-      </c>
-      <c r="M44" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M44" t="s">
+        <v>23</v>
       </c>
       <c r="N44" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O44" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D45" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E45" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G45" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H45" t="s">
+        <v>21</v>
       </c>
       <c r="I45" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J45">
         <v>1243</v>
@@ -3041,33 +3171,36 @@
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>112</v>
-      </c>
-      <c r="M45" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M45" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G46" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H46" t="s">
+        <v>21</v>
       </c>
       <c r="I46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J46">
         <v>1238</v>
@@ -3076,39 +3209,42 @@
         <v>7</v>
       </c>
       <c r="L46" t="s">
-        <v>112</v>
-      </c>
-      <c r="M46" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M46" t="s">
+        <v>23</v>
       </c>
       <c r="N46" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O46" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G47" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H47" t="s">
+        <v>21</v>
       </c>
       <c r="I47" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J47">
         <v>1242</v>
@@ -3117,39 +3253,42 @@
         <v>3</v>
       </c>
       <c r="L47" t="s">
-        <v>112</v>
-      </c>
-      <c r="M47" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M47" t="s">
+        <v>23</v>
       </c>
       <c r="N47" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O47" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E48" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G48" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H48" t="s">
+        <v>21</v>
       </c>
       <c r="I48" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J48">
         <v>1236</v>
@@ -3158,39 +3297,42 @@
         <v>9</v>
       </c>
       <c r="L48" t="s">
-        <v>112</v>
-      </c>
-      <c r="M48" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M48" t="s">
+        <v>23</v>
       </c>
       <c r="N48" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O48" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D49" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E49" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G49" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H49" t="s">
+        <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J49">
         <v>1236</v>
@@ -3199,42 +3341,42 @@
         <v>9</v>
       </c>
       <c r="L49" t="s">
-        <v>112</v>
-      </c>
-      <c r="M49" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M49" t="s">
+        <v>23</v>
       </c>
       <c r="N49" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O49" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G50" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I50" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J50">
         <v>1236</v>
@@ -3243,33 +3385,36 @@
         <v>9</v>
       </c>
       <c r="L50" t="s">
-        <v>112</v>
-      </c>
-      <c r="M50" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M50" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G51" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H51" t="s">
+        <v>21</v>
       </c>
       <c r="I51" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J51">
         <v>1245</v>
@@ -3278,33 +3423,33 @@
         <v>0</v>
       </c>
       <c r="L51" t="s">
-        <v>112</v>
-      </c>
-      <c r="M51" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M51" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E52" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H52" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I52" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J52">
         <v>1245</v>
@@ -3313,33 +3458,36 @@
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>112</v>
-      </c>
-      <c r="M52" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M52" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B53" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D53" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E53" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G53" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
       </c>
       <c r="J53">
         <v>1245</v>
@@ -3348,36 +3496,39 @@
         <v>0</v>
       </c>
       <c r="L53" t="s">
-        <v>112</v>
-      </c>
-      <c r="M53" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M53" t="s">
+        <v>23</v>
       </c>
       <c r="N53" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B54" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D54" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E54" t="s">
+        <v>88</v>
+      </c>
+      <c r="G54" t="s">
         <v>86</v>
       </c>
-      <c r="G54" t="s">
-        <v>84</v>
-      </c>
       <c r="H54" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
       </c>
       <c r="J54">
         <v>1245</v>
@@ -3386,36 +3537,39 @@
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>112</v>
-      </c>
-      <c r="M54" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M54" t="s">
+        <v>23</v>
       </c>
       <c r="N54" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D55" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E55" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G55" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
       </c>
       <c r="J55">
         <v>1245</v>
@@ -3424,36 +3578,39 @@
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>112</v>
-      </c>
-      <c r="M55" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M55" t="s">
+        <v>23</v>
       </c>
       <c r="N55" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D56" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G56" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
       </c>
       <c r="J56">
         <v>1245</v>
@@ -3462,36 +3619,39 @@
         <v>0</v>
       </c>
       <c r="L56" t="s">
-        <v>112</v>
-      </c>
-      <c r="M56" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M56" t="s">
+        <v>23</v>
       </c>
       <c r="N56" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D57" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E57" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G57" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
       </c>
       <c r="J57">
         <v>1245</v>
@@ -3500,36 +3660,39 @@
         <v>0</v>
       </c>
       <c r="L57" t="s">
-        <v>112</v>
-      </c>
-      <c r="M57" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M57" t="s">
+        <v>23</v>
       </c>
       <c r="N57" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D58" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E58" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G58" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
       </c>
       <c r="J58">
         <v>1245</v>
@@ -3538,36 +3701,39 @@
         <v>0</v>
       </c>
       <c r="L58" t="s">
-        <v>112</v>
-      </c>
-      <c r="M58" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M58" t="s">
+        <v>23</v>
       </c>
       <c r="N58" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D59" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E59" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G59" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
       </c>
       <c r="J59">
         <v>1245</v>
@@ -3576,36 +3742,39 @@
         <v>0</v>
       </c>
       <c r="L59" t="s">
-        <v>112</v>
-      </c>
-      <c r="M59" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M59" t="s">
+        <v>23</v>
       </c>
       <c r="N59" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D60" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E60" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G60" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
       </c>
       <c r="J60">
         <v>1245</v>
@@ -3614,36 +3783,39 @@
         <v>0</v>
       </c>
       <c r="L60" t="s">
-        <v>112</v>
-      </c>
-      <c r="M60" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M60" t="s">
+        <v>23</v>
       </c>
       <c r="N60" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D61" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E61" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G61" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H61" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
       </c>
       <c r="J61">
         <v>1245</v>
@@ -3652,33 +3824,36 @@
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>112</v>
-      </c>
-      <c r="M61" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M61" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" t="s">
+        <v>112</v>
+      </c>
+      <c r="C62" t="s">
+        <v>106</v>
+      </c>
+      <c r="D62" t="s">
+        <v>146</v>
+      </c>
+      <c r="E62" t="s">
         <v>109</v>
       </c>
-      <c r="B62" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" t="s">
-        <v>104</v>
-      </c>
-      <c r="D62" t="s">
-        <v>144</v>
-      </c>
-      <c r="E62" t="s">
-        <v>107</v>
-      </c>
       <c r="G62" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
       </c>
       <c r="J62">
         <v>1245</v>
@@ -3687,33 +3862,36 @@
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>112</v>
-      </c>
-      <c r="M62" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M62" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B63" t="s">
+        <v>112</v>
+      </c>
+      <c r="C63" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63" t="s">
         <v>110</v>
       </c>
-      <c r="C63" t="s">
-        <v>104</v>
-      </c>
-      <c r="D63" t="s">
-        <v>144</v>
-      </c>
-      <c r="E63" t="s">
-        <v>108</v>
-      </c>
       <c r="G63" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H63" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
       </c>
       <c r="J63">
         <v>1245</v>
@@ -3722,18 +3900,18 @@
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>112</v>
-      </c>
-      <c r="M63" t="b">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="M63" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
@@ -3748,7 +3926,10 @@
         <v>19</v>
       </c>
       <c r="H64" t="s">
-        <v>147</v>
+        <v>149</v>
+      </c>
+      <c r="I64" t="s">
+        <v>21</v>
       </c>
       <c r="J64">
         <v>9125</v>
@@ -3756,31 +3937,34 @@
       <c r="K64">
         <v>0</v>
       </c>
-      <c r="M64" t="b">
-        <v>1</v>
+      <c r="M64" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E65" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G65" t="s">
         <v>19</v>
       </c>
       <c r="H65" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="I65" t="s">
+        <v>21</v>
       </c>
       <c r="J65">
         <v>9125</v>
@@ -3788,31 +3972,34 @@
       <c r="K65">
         <v>0</v>
       </c>
-      <c r="M65" t="b">
-        <v>1</v>
+      <c r="M65" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B66" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G66" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H66" t="s">
+        <v>21</v>
       </c>
       <c r="I66" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J66">
         <v>9125</v>
@@ -3820,31 +4007,34 @@
       <c r="K66">
         <v>0</v>
       </c>
-      <c r="M66" t="b">
-        <v>1</v>
+      <c r="M66" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D67" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E67" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G67" t="s">
         <v>19</v>
       </c>
       <c r="H67" t="s">
-        <v>150</v>
+        <v>152</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
       </c>
       <c r="J67">
         <v>9124</v>
@@ -3852,34 +4042,34 @@
       <c r="K67">
         <v>1</v>
       </c>
-      <c r="M67" t="b">
-        <v>1</v>
+      <c r="M67" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C68" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D68" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E68" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G68" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H68" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I68" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J68">
         <v>9107</v>
@@ -3887,40 +4077,40 @@
       <c r="K68">
         <v>18</v>
       </c>
-      <c r="M68" t="b">
-        <v>1</v>
+      <c r="M68" t="s">
+        <v>23</v>
       </c>
       <c r="N68" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O68" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D69" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E69" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G69" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H69" t="s">
+        <v>157</v>
+      </c>
+      <c r="I69" t="s">
         <v>155</v>
-      </c>
-      <c r="I69" t="s">
-        <v>153</v>
       </c>
       <c r="J69">
         <v>9119</v>
@@ -3928,40 +4118,40 @@
       <c r="K69">
         <v>6</v>
       </c>
-      <c r="M69" t="b">
-        <v>1</v>
+      <c r="M69" t="s">
+        <v>23</v>
       </c>
       <c r="N69" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O69" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B70" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C70" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D70" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E70" t="s">
+        <v>159</v>
+      </c>
+      <c r="G70" t="s">
+        <v>36</v>
+      </c>
+      <c r="H70" t="s">
         <v>157</v>
       </c>
-      <c r="G70" t="s">
-        <v>34</v>
-      </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>155</v>
-      </c>
-      <c r="I70" t="s">
-        <v>153</v>
       </c>
       <c r="J70">
         <v>9118</v>
@@ -3969,40 +4159,40 @@
       <c r="K70">
         <v>7</v>
       </c>
-      <c r="M70" t="b">
-        <v>1</v>
+      <c r="M70" t="s">
+        <v>23</v>
       </c>
       <c r="N70" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O70" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D71" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E71" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G71" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H71" t="s">
+        <v>157</v>
+      </c>
+      <c r="I71" t="s">
         <v>155</v>
-      </c>
-      <c r="I71" t="s">
-        <v>153</v>
       </c>
       <c r="J71">
         <v>9116</v>
@@ -4010,40 +4200,40 @@
       <c r="K71">
         <v>9</v>
       </c>
-      <c r="M71" t="b">
-        <v>1</v>
+      <c r="M71" t="s">
+        <v>23</v>
       </c>
       <c r="N71" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O71" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C72" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D72" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E72" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G72" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H72" t="s">
+        <v>157</v>
+      </c>
+      <c r="I72" t="s">
         <v>155</v>
-      </c>
-      <c r="I72" t="s">
-        <v>153</v>
       </c>
       <c r="J72">
         <v>9110</v>
@@ -4051,37 +4241,37 @@
       <c r="K72">
         <v>15</v>
       </c>
-      <c r="M72" t="b">
-        <v>1</v>
+      <c r="M72" t="s">
+        <v>23</v>
       </c>
       <c r="N72" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C73" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D73" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G73" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H73" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I73" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J73">
         <v>9109</v>
@@ -4089,37 +4279,37 @@
       <c r="K73">
         <v>16</v>
       </c>
-      <c r="M73" t="b">
-        <v>1</v>
+      <c r="M73" t="s">
+        <v>23</v>
       </c>
       <c r="N73" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C74" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D74" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E74" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G74" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H74" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I74" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J74">
         <v>9097</v>
@@ -4127,40 +4317,40 @@
       <c r="K74">
         <v>28</v>
       </c>
-      <c r="M74" t="b">
-        <v>1</v>
+      <c r="M74" t="s">
+        <v>23</v>
       </c>
       <c r="N74" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O74" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C75" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D75" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E75" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G75" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H75" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I75" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J75">
         <v>9121</v>
@@ -4168,37 +4358,37 @@
       <c r="K75">
         <v>4</v>
       </c>
-      <c r="M75" t="b">
-        <v>1</v>
+      <c r="M75" t="s">
+        <v>23</v>
       </c>
       <c r="N75" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B76" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D76" t="s">
+        <v>168</v>
+      </c>
+      <c r="E76" t="s">
+        <v>168</v>
+      </c>
+      <c r="G76" t="s">
+        <v>36</v>
+      </c>
+      <c r="H76" t="s">
         <v>166</v>
       </c>
-      <c r="E76" t="s">
-        <v>166</v>
-      </c>
-      <c r="G76" t="s">
-        <v>34</v>
-      </c>
-      <c r="H76" t="s">
-        <v>164</v>
-      </c>
       <c r="I76" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J76">
         <v>9124</v>
@@ -4206,37 +4396,37 @@
       <c r="K76">
         <v>1</v>
       </c>
-      <c r="M76" t="b">
-        <v>1</v>
+      <c r="M76" t="s">
+        <v>23</v>
       </c>
       <c r="N76" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B77" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C77" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E77" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G77" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H77" t="s">
+        <v>157</v>
+      </c>
+      <c r="I77" t="s">
         <v>155</v>
-      </c>
-      <c r="I77" t="s">
-        <v>153</v>
       </c>
       <c r="J77">
         <v>9075</v>
@@ -4244,34 +4434,37 @@
       <c r="K77">
         <v>50</v>
       </c>
-      <c r="M77" t="b">
-        <v>1</v>
+      <c r="M77" t="s">
+        <v>23</v>
       </c>
       <c r="N77" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O77" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B78" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C78" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E78" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G78" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H78" t="s">
+        <v>21</v>
       </c>
       <c r="I78" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J78">
         <v>9124</v>
@@ -4279,16 +4472,16 @@
       <c r="K78">
         <v>1</v>
       </c>
-      <c r="M78" t="b">
-        <v>1</v>
+      <c r="M78" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B79" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
@@ -4303,7 +4496,10 @@
         <v>19</v>
       </c>
       <c r="H79" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
       </c>
       <c r="J79">
         <v>5983</v>
@@ -4311,31 +4507,34 @@
       <c r="K79">
         <v>0</v>
       </c>
-      <c r="M79" t="b">
-        <v>1</v>
+      <c r="M79" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E80" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G80" t="s">
         <v>19</v>
       </c>
       <c r="H80" t="s">
-        <v>172</v>
+        <v>174</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
       </c>
       <c r="J80">
         <v>5983</v>
@@ -4343,31 +4542,34 @@
       <c r="K80">
         <v>0</v>
       </c>
-      <c r="M80" t="b">
-        <v>1</v>
+      <c r="M80" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G81" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H81" t="s">
+        <v>21</v>
       </c>
       <c r="I81" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J81">
         <v>5983</v>
@@ -4375,31 +4577,34 @@
       <c r="K81">
         <v>0</v>
       </c>
-      <c r="M81" t="b">
-        <v>1</v>
+      <c r="M81" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E82" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G82" t="s">
         <v>19</v>
       </c>
       <c r="H82" t="s">
-        <v>175</v>
+        <v>177</v>
+      </c>
+      <c r="I82" t="s">
+        <v>21</v>
       </c>
       <c r="J82">
         <v>5980</v>
@@ -4407,31 +4612,34 @@
       <c r="K82">
         <v>3</v>
       </c>
-      <c r="M82" t="b">
-        <v>1</v>
+      <c r="M82" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D83" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E83" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G83" t="s">
         <v>19</v>
       </c>
       <c r="H83" t="s">
-        <v>177</v>
+        <v>179</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
       </c>
       <c r="J83">
         <v>5980</v>
@@ -4439,31 +4647,34 @@
       <c r="K83">
         <v>3</v>
       </c>
-      <c r="M83" t="b">
-        <v>1</v>
+      <c r="M83" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B84" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C84" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G84" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H84" t="s">
+        <v>21</v>
       </c>
       <c r="I84" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J84">
         <v>5958</v>
@@ -4471,34 +4682,37 @@
       <c r="K84">
         <v>25</v>
       </c>
-      <c r="M84" t="b">
-        <v>1</v>
+      <c r="M84" t="s">
+        <v>23</v>
       </c>
       <c r="N84" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B85" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D85" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E85" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G85" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H85" t="s">
+        <v>21</v>
       </c>
       <c r="I85" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J85">
         <v>5980</v>
@@ -4506,25 +4720,31 @@
       <c r="K85">
         <v>3</v>
       </c>
-      <c r="M85" t="b">
-        <v>1</v>
+      <c r="M85" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B86" t="s">
-        <v>170</v>
+        <v>172</v>
+      </c>
+      <c r="C86" t="s">
+        <v>34</v>
       </c>
       <c r="E86" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G86" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H86" t="s">
+        <v>21</v>
       </c>
       <c r="I86" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J86">
         <v>5978</v>
@@ -4532,25 +4752,31 @@
       <c r="K86">
         <v>5</v>
       </c>
-      <c r="M86" t="b">
-        <v>1</v>
+      <c r="M86" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B87" t="s">
-        <v>170</v>
+        <v>172</v>
+      </c>
+      <c r="C87" t="s">
+        <v>80</v>
       </c>
       <c r="E87" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G87" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H87" t="s">
+        <v>21</v>
       </c>
       <c r="I87" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J87">
         <v>5980</v>
@@ -4558,31 +4784,34 @@
       <c r="K87">
         <v>3</v>
       </c>
-      <c r="M87" t="b">
-        <v>1</v>
+      <c r="M87" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B88" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C88" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D88" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E88" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G88" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H88" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
       </c>
       <c r="J88">
         <v>5983</v>
@@ -4590,34 +4819,37 @@
       <c r="K88">
         <v>0</v>
       </c>
-      <c r="M88" t="b">
-        <v>1</v>
+      <c r="M88" t="s">
+        <v>23</v>
       </c>
       <c r="N88" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C89" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D89" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E89" t="s">
+        <v>88</v>
+      </c>
+      <c r="G89" t="s">
         <v>86</v>
       </c>
-      <c r="G89" t="s">
-        <v>84</v>
-      </c>
       <c r="H89" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I89" t="s">
+        <v>21</v>
       </c>
       <c r="J89">
         <v>5983</v>
@@ -4625,34 +4857,37 @@
       <c r="K89">
         <v>0</v>
       </c>
-      <c r="M89" t="b">
-        <v>1</v>
+      <c r="M89" t="s">
+        <v>23</v>
       </c>
       <c r="N89" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B90" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C90" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D90" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E90" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G90" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H90" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
       </c>
       <c r="J90">
         <v>5983</v>
@@ -4660,34 +4895,37 @@
       <c r="K90">
         <v>0</v>
       </c>
-      <c r="M90" t="b">
-        <v>1</v>
+      <c r="M90" t="s">
+        <v>23</v>
       </c>
       <c r="N90" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B91" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C91" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D91" t="s">
+        <v>91</v>
+      </c>
+      <c r="E91" t="s">
+        <v>93</v>
+      </c>
+      <c r="G91" t="s">
+        <v>86</v>
+      </c>
+      <c r="H91" t="s">
         <v>89</v>
       </c>
-      <c r="E91" t="s">
-        <v>91</v>
-      </c>
-      <c r="G91" t="s">
-        <v>84</v>
-      </c>
-      <c r="H91" t="s">
-        <v>87</v>
+      <c r="I91" t="s">
+        <v>21</v>
       </c>
       <c r="J91">
         <v>5983</v>
@@ -4695,34 +4933,37 @@
       <c r="K91">
         <v>0</v>
       </c>
-      <c r="M91" t="b">
-        <v>1</v>
+      <c r="M91" t="s">
+        <v>23</v>
       </c>
       <c r="N91" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C92" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D92" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E92" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G92" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H92" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
       </c>
       <c r="J92">
         <v>5983</v>
@@ -4730,34 +4971,37 @@
       <c r="K92">
         <v>0</v>
       </c>
-      <c r="M92" t="b">
-        <v>1</v>
+      <c r="M92" t="s">
+        <v>23</v>
       </c>
       <c r="N92" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B93" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C93" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D93" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E93" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G93" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H93" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
       </c>
       <c r="J93">
         <v>5983</v>
@@ -4765,34 +5009,37 @@
       <c r="K93">
         <v>0</v>
       </c>
-      <c r="M93" t="b">
-        <v>1</v>
+      <c r="M93" t="s">
+        <v>23</v>
       </c>
       <c r="N93" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B94" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D94" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E94" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G94" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H94" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I94" t="s">
+        <v>21</v>
       </c>
       <c r="J94">
         <v>5983</v>
@@ -4800,34 +5047,37 @@
       <c r="K94">
         <v>0</v>
       </c>
-      <c r="M94" t="b">
-        <v>1</v>
+      <c r="M94" t="s">
+        <v>23</v>
       </c>
       <c r="N94" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D95" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E95" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G95" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H95" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I95" t="s">
+        <v>21</v>
       </c>
       <c r="J95">
         <v>5983</v>
@@ -4835,34 +5085,37 @@
       <c r="K95">
         <v>0</v>
       </c>
-      <c r="M95" t="b">
-        <v>1</v>
+      <c r="M95" t="s">
+        <v>23</v>
       </c>
       <c r="N95" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B96" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C96" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E96" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G96" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H96" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I96" t="s">
+        <v>21</v>
       </c>
       <c r="J96">
         <v>5983</v>
@@ -4870,34 +5123,37 @@
       <c r="K96">
         <v>0</v>
       </c>
-      <c r="M96" t="b">
-        <v>1</v>
+      <c r="M96" t="s">
+        <v>23</v>
       </c>
       <c r="N96" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B97" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C97" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D97" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E97" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G97" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H97" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I97" t="s">
+        <v>21</v>
       </c>
       <c r="J97">
         <v>5983</v>
@@ -4905,34 +5161,37 @@
       <c r="K97">
         <v>0</v>
       </c>
-      <c r="M97" t="b">
-        <v>1</v>
+      <c r="M97" t="s">
+        <v>23</v>
       </c>
       <c r="N97" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B98" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C98" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D98" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E98" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G98" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H98" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I98" t="s">
+        <v>21</v>
       </c>
       <c r="J98">
         <v>5983</v>
@@ -4940,34 +5199,37 @@
       <c r="K98">
         <v>0</v>
       </c>
-      <c r="M98" t="b">
-        <v>1</v>
+      <c r="M98" t="s">
+        <v>23</v>
       </c>
       <c r="N98" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B99" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C99" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D99" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E99" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G99" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H99" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I99" t="s">
+        <v>21</v>
       </c>
       <c r="J99">
         <v>5983</v>
@@ -4975,34 +5237,37 @@
       <c r="K99">
         <v>0</v>
       </c>
-      <c r="M99" t="b">
-        <v>1</v>
+      <c r="M99" t="s">
+        <v>23</v>
       </c>
       <c r="N99" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B100" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C100" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D100" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E100" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G100" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H100" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I100" t="s">
+        <v>21</v>
       </c>
       <c r="J100">
         <v>5983</v>
@@ -5010,19 +5275,19 @@
       <c r="K100">
         <v>0</v>
       </c>
-      <c r="M100" t="b">
-        <v>1</v>
+      <c r="M100" t="s">
+        <v>23</v>
       </c>
       <c r="N100" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B101" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C101" t="s">
         <v>17</v>
@@ -5037,7 +5302,10 @@
         <v>19</v>
       </c>
       <c r="H101" t="s">
-        <v>185</v>
+        <v>187</v>
+      </c>
+      <c r="I101" t="s">
+        <v>21</v>
       </c>
       <c r="J101">
         <v>11848</v>
@@ -5045,31 +5313,34 @@
       <c r="K101">
         <v>0</v>
       </c>
-      <c r="M101" t="b">
-        <v>1</v>
+      <c r="M101" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C102" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D102" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E102" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G102" t="s">
         <v>19</v>
       </c>
       <c r="H102" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="I102" t="s">
+        <v>21</v>
       </c>
       <c r="J102">
         <v>11848</v>
@@ -5077,31 +5348,34 @@
       <c r="K102">
         <v>0</v>
       </c>
-      <c r="M102" t="b">
-        <v>1</v>
+      <c r="M102" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B103" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C103" t="s">
         <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E103" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G103" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H103" t="s">
+        <v>21</v>
       </c>
       <c r="I103" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J103">
         <v>11848</v>
@@ -5109,31 +5383,34 @@
       <c r="K103">
         <v>0</v>
       </c>
-      <c r="M103" t="b">
-        <v>1</v>
+      <c r="M103" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B104" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C104" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D104" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E104" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G104" t="s">
         <v>19</v>
       </c>
       <c r="H104" t="s">
-        <v>187</v>
+        <v>189</v>
+      </c>
+      <c r="I104" t="s">
+        <v>21</v>
       </c>
       <c r="J104">
         <v>11845</v>
@@ -5141,31 +5418,34 @@
       <c r="K104">
         <v>3</v>
       </c>
-      <c r="M104" t="b">
-        <v>1</v>
+      <c r="M104" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D105" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E105" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G105" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H105" t="s">
+        <v>21</v>
       </c>
       <c r="I105" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J105">
         <v>11848</v>
@@ -5173,34 +5453,37 @@
       <c r="K105">
         <v>0</v>
       </c>
-      <c r="M105" t="b">
-        <v>1</v>
+      <c r="M105" t="s">
+        <v>23</v>
       </c>
       <c r="N105" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O105" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B106" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C106" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E106" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G106" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H106" t="s">
+        <v>21</v>
       </c>
       <c r="I106" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J106">
         <v>11845</v>
@@ -5208,16 +5491,16 @@
       <c r="K106">
         <v>3</v>
       </c>
-      <c r="M106" t="b">
-        <v>1</v>
+      <c r="M106" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B107" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C107" t="s">
         <v>17</v>
@@ -5232,7 +5515,10 @@
         <v>19</v>
       </c>
       <c r="H107" t="s">
-        <v>193</v>
+        <v>195</v>
+      </c>
+      <c r="I107" t="s">
+        <v>21</v>
       </c>
       <c r="J107">
         <v>2697</v>
@@ -5241,33 +5527,36 @@
         <v>0</v>
       </c>
       <c r="L107" t="s">
-        <v>194</v>
-      </c>
-      <c r="M107" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="M107" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D108" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E108" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G108" t="s">
         <v>19</v>
       </c>
       <c r="H108" t="s">
-        <v>195</v>
+        <v>197</v>
+      </c>
+      <c r="I108" t="s">
+        <v>21</v>
       </c>
       <c r="J108">
         <v>2697</v>
@@ -5276,33 +5565,36 @@
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>194</v>
-      </c>
-      <c r="M108" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="M108" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C109" t="s">
         <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E109" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G109" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H109" t="s">
+        <v>21</v>
       </c>
       <c r="I109" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J109">
         <v>2697</v>
@@ -5311,33 +5603,36 @@
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>194</v>
-      </c>
-      <c r="M109" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="M109" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B110" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C110" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D110" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G110" t="s">
         <v>19</v>
       </c>
       <c r="H110" t="s">
-        <v>197</v>
+        <v>199</v>
+      </c>
+      <c r="I110" t="s">
+        <v>21</v>
       </c>
       <c r="J110">
         <v>2697</v>
@@ -5346,36 +5641,36 @@
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>194</v>
-      </c>
-      <c r="M110" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="M110" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B111" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C111" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D111" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E111" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G111" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H111" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I111" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J111">
         <v>2697</v>
@@ -5384,30 +5679,33 @@
         <v>0</v>
       </c>
       <c r="L111" t="s">
-        <v>194</v>
-      </c>
-      <c r="M111" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="M111" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B112" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C112" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E112" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G112" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H112" t="s">
+        <v>21</v>
       </c>
       <c r="I112" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J112">
         <v>2697</v>
@@ -5416,33 +5714,36 @@
         <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>194</v>
-      </c>
-      <c r="M112" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="M112" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B113" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C113" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D113" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E113" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G113" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H113" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="I113" t="s">
+        <v>21</v>
       </c>
       <c r="J113">
         <v>2697</v>
@@ -5451,33 +5752,36 @@
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>194</v>
-      </c>
-      <c r="M113" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="M113" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B114" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C114" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D114" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E114" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G114" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H114" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I114" t="s">
+        <v>21</v>
       </c>
       <c r="J114">
         <v>2697</v>
@@ -5486,33 +5790,36 @@
         <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>194</v>
-      </c>
-      <c r="M114" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="M114" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B115" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C115" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D115" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E115" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G115" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H115" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="I115" t="s">
+        <v>21</v>
       </c>
       <c r="J115">
         <v>2697</v>
@@ -5521,33 +5828,36 @@
         <v>0</v>
       </c>
       <c r="L115" t="s">
-        <v>194</v>
-      </c>
-      <c r="M115" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="M115" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B116" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C116" t="s">
         <v>17</v>
       </c>
       <c r="D116" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G116" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H116" t="s">
+        <v>21</v>
       </c>
       <c r="I116" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J116">
         <v>455</v>
@@ -5556,33 +5866,36 @@
         <v>0</v>
       </c>
       <c r="L116" t="s">
-        <v>206</v>
-      </c>
-      <c r="M116" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M116" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B117" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C117" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D117" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E117" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G117" t="s">
         <v>19</v>
       </c>
       <c r="H117" t="s">
-        <v>207</v>
+        <v>209</v>
+      </c>
+      <c r="I117" t="s">
+        <v>21</v>
       </c>
       <c r="J117">
         <v>455</v>
@@ -5591,33 +5904,36 @@
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>206</v>
-      </c>
-      <c r="M117" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M117" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B118" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C118" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D118" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E118" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G118" t="s">
         <v>19</v>
       </c>
       <c r="H118" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="I118" t="s">
+        <v>21</v>
       </c>
       <c r="J118">
         <v>455</v>
@@ -5626,36 +5942,39 @@
         <v>0</v>
       </c>
       <c r="L118" t="s">
-        <v>206</v>
-      </c>
-      <c r="M118" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M118" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C119" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D119" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E119" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F119" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G119" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H119" t="s">
+        <v>21</v>
       </c>
       <c r="I119" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J119">
         <v>455</v>
@@ -5664,42 +5983,45 @@
         <v>0</v>
       </c>
       <c r="L119" t="s">
-        <v>206</v>
-      </c>
-      <c r="M119" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M119" t="s">
+        <v>23</v>
       </c>
       <c r="N119" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O119" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B120" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C120" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D120" t="s">
+        <v>216</v>
+      </c>
+      <c r="E120" t="s">
+        <v>76</v>
+      </c>
+      <c r="F120" t="s">
         <v>214</v>
       </c>
-      <c r="E120" t="s">
-        <v>74</v>
-      </c>
-      <c r="F120" t="s">
-        <v>212</v>
-      </c>
       <c r="G120" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H120" t="s">
+        <v>21</v>
       </c>
       <c r="I120" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J120">
         <v>455</v>
@@ -5708,42 +6030,45 @@
         <v>0</v>
       </c>
       <c r="L120" t="s">
-        <v>206</v>
-      </c>
-      <c r="M120" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M120" t="s">
+        <v>23</v>
       </c>
       <c r="N120" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O120" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B121" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C121" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D121" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E121" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F121" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G121" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H121" t="s">
+        <v>21</v>
       </c>
       <c r="I121" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J121">
         <v>455</v>
@@ -5752,42 +6077,45 @@
         <v>0</v>
       </c>
       <c r="L121" t="s">
-        <v>206</v>
-      </c>
-      <c r="M121" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M121" t="s">
+        <v>23</v>
       </c>
       <c r="N121" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O121" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B122" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C122" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D122" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E122" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F122" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G122" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H122" t="s">
+        <v>21</v>
       </c>
       <c r="I122" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J122">
         <v>455</v>
@@ -5796,42 +6124,45 @@
         <v>0</v>
       </c>
       <c r="L122" t="s">
-        <v>206</v>
-      </c>
-      <c r="M122" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M122" t="s">
+        <v>23</v>
       </c>
       <c r="N122" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O122" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B123" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C123" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D123" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E123" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F123" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G123" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H123" t="s">
+        <v>21</v>
       </c>
       <c r="I123" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J123">
         <v>455</v>
@@ -5840,42 +6171,45 @@
         <v>0</v>
       </c>
       <c r="L123" t="s">
-        <v>206</v>
-      </c>
-      <c r="M123" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M123" t="s">
+        <v>23</v>
       </c>
       <c r="N123" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O123" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B124" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C124" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D124" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E124" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F124" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G124" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H124" t="s">
+        <v>21</v>
       </c>
       <c r="I124" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J124">
         <v>455</v>
@@ -5884,42 +6218,45 @@
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>206</v>
-      </c>
-      <c r="M124" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M124" t="s">
+        <v>23</v>
       </c>
       <c r="N124" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O124" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B125" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C125" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D125" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E125" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F125" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G125" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H125" t="s">
+        <v>21</v>
       </c>
       <c r="I125" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J125">
         <v>455</v>
@@ -5928,42 +6265,45 @@
         <v>0</v>
       </c>
       <c r="L125" t="s">
-        <v>206</v>
-      </c>
-      <c r="M125" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M125" t="s">
+        <v>23</v>
       </c>
       <c r="N125" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O125" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B126" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C126" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D126" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E126" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F126" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G126" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H126" t="s">
+        <v>21</v>
       </c>
       <c r="I126" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J126">
         <v>455</v>
@@ -5972,42 +6312,45 @@
         <v>0</v>
       </c>
       <c r="L126" t="s">
-        <v>206</v>
-      </c>
-      <c r="M126" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M126" t="s">
+        <v>23</v>
       </c>
       <c r="N126" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O126" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B127" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C127" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D127" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E127" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F127" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G127" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H127" t="s">
+        <v>21</v>
       </c>
       <c r="I127" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J127">
         <v>455</v>
@@ -6016,42 +6359,45 @@
         <v>0</v>
       </c>
       <c r="L127" t="s">
-        <v>206</v>
-      </c>
-      <c r="M127" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M127" t="s">
+        <v>23</v>
       </c>
       <c r="N127" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O127" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B128" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C128" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D128" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E128" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F128" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G128" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H128" t="s">
+        <v>21</v>
       </c>
       <c r="I128" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J128">
         <v>455</v>
@@ -6060,42 +6406,45 @@
         <v>0</v>
       </c>
       <c r="L128" t="s">
-        <v>206</v>
-      </c>
-      <c r="M128" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M128" t="s">
+        <v>23</v>
       </c>
       <c r="N128" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O128" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B129" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C129" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D129" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E129" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F129" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G129" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H129" t="s">
+        <v>21</v>
       </c>
       <c r="I129" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J129">
         <v>455</v>
@@ -6104,36 +6453,39 @@
         <v>0</v>
       </c>
       <c r="L129" t="s">
-        <v>206</v>
-      </c>
-      <c r="M129" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M129" t="s">
+        <v>23</v>
       </c>
       <c r="N129" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O129" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B130" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C130" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E130" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G130" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H130" t="s">
+        <v>21</v>
       </c>
       <c r="I130" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J130">
         <v>455</v>
@@ -6142,36 +6494,36 @@
         <v>0</v>
       </c>
       <c r="L130" t="s">
-        <v>206</v>
-      </c>
-      <c r="M130" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="M130" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B131" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C131" t="s">
         <v>17</v>
       </c>
       <c r="D131" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G131" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H131" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I131" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J131">
         <v>4190</v>
@@ -6180,27 +6532,27 @@
         <v>0</v>
       </c>
       <c r="L131" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M131" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B132" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C132" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D132" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E132" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G132" t="s">
         <v>19</v>
@@ -6209,7 +6561,7 @@
         <v>250</v>
       </c>
       <c r="I132" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="J132">
         <v>4190</v>
@@ -6218,27 +6570,27 @@
         <v>0</v>
       </c>
       <c r="L132" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M132" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B133" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C133" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D133" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E133" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G133" t="s">
         <v>19</v>
@@ -6247,7 +6599,7 @@
         <v>251</v>
       </c>
       <c r="I133" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="J133">
         <v>4190</v>
@@ -6256,36 +6608,36 @@
         <v>0</v>
       </c>
       <c r="L133" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M133" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B134" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C134" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D134" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E134" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F134" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G134" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H134" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I134" t="s">
         <v>252</v>
@@ -6297,42 +6649,42 @@
         <v>0</v>
       </c>
       <c r="L134" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M134" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N134" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O134" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B135" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C135" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D135" t="s">
+        <v>216</v>
+      </c>
+      <c r="E135" t="s">
+        <v>76</v>
+      </c>
+      <c r="F135" t="s">
         <v>214</v>
       </c>
-      <c r="E135" t="s">
-        <v>74</v>
-      </c>
-      <c r="F135" t="s">
-        <v>212</v>
-      </c>
       <c r="G135" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H135" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I135" t="s">
         <v>253</v>
@@ -6344,42 +6696,42 @@
         <v>1</v>
       </c>
       <c r="L135" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M135" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N135" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O135" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B136" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C136" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D136" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E136" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F136" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G136" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H136" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I136" t="s">
         <v>254</v>
@@ -6391,42 +6743,42 @@
         <v>0</v>
       </c>
       <c r="L136" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M136" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N136" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O136" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B137" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C137" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D137" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E137" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F137" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G137" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H137" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I137" t="s">
         <v>255</v>
@@ -6438,42 +6790,42 @@
         <v>2</v>
       </c>
       <c r="L137" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M137" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N137" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O137" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B138" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C138" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D138" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E138" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F138" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G138" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H138" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I138" t="s">
         <v>256</v>
@@ -6485,42 +6837,42 @@
         <v>0</v>
       </c>
       <c r="L138" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M138" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N138" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O138" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B139" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C139" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D139" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E139" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F139" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G139" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H139" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I139" t="s">
         <v>257</v>
@@ -6532,42 +6884,42 @@
         <v>1</v>
       </c>
       <c r="L139" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M139" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N139" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O139" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B140" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C140" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D140" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E140" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F140" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G140" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H140" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I140" t="s">
         <v>258</v>
@@ -6579,42 +6931,42 @@
         <v>1</v>
       </c>
       <c r="L140" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M140" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N140" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O140" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B141" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C141" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D141" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E141" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F141" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G141" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H141" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I141" t="s">
         <v>259</v>
@@ -6626,42 +6978,42 @@
         <v>0</v>
       </c>
       <c r="L141" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M141" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N141" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O141" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B142" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C142" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D142" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E142" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F142" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G142" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H142" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I142" t="s">
         <v>260</v>
@@ -6673,42 +7025,42 @@
         <v>0</v>
       </c>
       <c r="L142" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M142" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N142" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O142" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B143" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C143" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D143" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E143" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F143" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G143" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H143" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I143" t="s">
         <v>261</v>
@@ -6720,42 +7072,42 @@
         <v>0</v>
       </c>
       <c r="L143" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M143" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N143" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O143" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B144" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C144" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D144" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E144" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F144" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G144" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H144" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I144" t="s">
         <v>262</v>
@@ -6767,36 +7119,36 @@
         <v>1</v>
       </c>
       <c r="L144" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M144" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c r="N144" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O144" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B145" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E145" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G145" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H145" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="I145" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J145">
         <v>4190</v>
@@ -6805,10 +7157,10 @@
         <v>0</v>
       </c>
       <c r="L145" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M145" t="s">
-        <v>249</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.3">
@@ -6822,13 +7174,16 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E146" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G146" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H146" t="s">
+        <v>21</v>
       </c>
       <c r="I146" t="s">
         <v>265</v>
@@ -6842,8 +7197,8 @@
       <c r="L146" t="s">
         <v>266</v>
       </c>
-      <c r="M146" t="b">
-        <v>1</v>
+      <c r="M146" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.3">
@@ -6854,13 +7209,13 @@
         <v>264</v>
       </c>
       <c r="C147" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D147" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E147" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G147" t="s">
         <v>19</v>
@@ -6868,6 +7223,9 @@
       <c r="H147" t="s">
         <v>267</v>
       </c>
+      <c r="I147" t="s">
+        <v>21</v>
+      </c>
       <c r="J147">
         <v>1725</v>
       </c>
@@ -6877,8 +7235,8 @@
       <c r="L147" t="s">
         <v>266</v>
       </c>
-      <c r="M147" t="b">
-        <v>1</v>
+      <c r="M147" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.3">
@@ -6889,13 +7247,13 @@
         <v>264</v>
       </c>
       <c r="C148" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D148" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E148" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G148" t="s">
         <v>19</v>
@@ -6903,6 +7261,9 @@
       <c r="H148" t="s">
         <v>268</v>
       </c>
+      <c r="I148" t="s">
+        <v>21</v>
+      </c>
       <c r="J148">
         <v>1725</v>
       </c>
@@ -6912,8 +7273,8 @@
       <c r="L148" t="s">
         <v>266</v>
       </c>
-      <c r="M148" t="b">
-        <v>1</v>
+      <c r="M148" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.3">
@@ -6924,13 +7285,13 @@
         <v>264</v>
       </c>
       <c r="C149" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D149" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E149" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G149" t="s">
         <v>19</v>
@@ -6938,6 +7299,9 @@
       <c r="H149" t="s">
         <v>269</v>
       </c>
+      <c r="I149" t="s">
+        <v>21</v>
+      </c>
       <c r="J149">
         <v>1725</v>
       </c>
@@ -6947,8 +7311,8 @@
       <c r="L149" t="s">
         <v>266</v>
       </c>
-      <c r="M149" t="b">
-        <v>1</v>
+      <c r="M149" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.3">
@@ -6959,19 +7323,22 @@
         <v>264</v>
       </c>
       <c r="C150" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D150" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E150" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F150" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G150" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H150" t="s">
+        <v>21</v>
       </c>
       <c r="I150" t="s">
         <v>270</v>
@@ -6985,14 +7352,14 @@
       <c r="L150" t="s">
         <v>266</v>
       </c>
-      <c r="M150" t="b">
-        <v>1</v>
+      <c r="M150" t="s">
+        <v>23</v>
       </c>
       <c r="N150" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O150" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
@@ -7003,19 +7370,22 @@
         <v>264</v>
       </c>
       <c r="C151" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D151" t="s">
+        <v>216</v>
+      </c>
+      <c r="E151" t="s">
+        <v>76</v>
+      </c>
+      <c r="F151" t="s">
         <v>214</v>
       </c>
-      <c r="E151" t="s">
-        <v>74</v>
-      </c>
-      <c r="F151" t="s">
-        <v>212</v>
-      </c>
       <c r="G151" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H151" t="s">
+        <v>21</v>
       </c>
       <c r="I151" t="s">
         <v>271</v>
@@ -7029,14 +7399,14 @@
       <c r="L151" t="s">
         <v>266</v>
       </c>
-      <c r="M151" t="b">
-        <v>1</v>
+      <c r="M151" t="s">
+        <v>23</v>
       </c>
       <c r="N151" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O151" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.3">
@@ -7047,19 +7417,22 @@
         <v>264</v>
       </c>
       <c r="C152" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D152" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E152" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F152" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G152" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H152" t="s">
+        <v>21</v>
       </c>
       <c r="I152" t="s">
         <v>272</v>
@@ -7073,14 +7446,14 @@
       <c r="L152" t="s">
         <v>266</v>
       </c>
-      <c r="M152" t="b">
-        <v>1</v>
+      <c r="M152" t="s">
+        <v>23</v>
       </c>
       <c r="N152" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O152" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.3">
@@ -7091,19 +7464,22 @@
         <v>264</v>
       </c>
       <c r="C153" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D153" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E153" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F153" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G153" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H153" t="s">
+        <v>21</v>
       </c>
       <c r="I153" t="s">
         <v>273</v>
@@ -7117,14 +7493,14 @@
       <c r="L153" t="s">
         <v>266</v>
       </c>
-      <c r="M153" t="b">
-        <v>1</v>
+      <c r="M153" t="s">
+        <v>23</v>
       </c>
       <c r="N153" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O153" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.3">
@@ -7135,19 +7511,22 @@
         <v>264</v>
       </c>
       <c r="C154" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D154" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E154" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F154" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G154" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H154" t="s">
+        <v>21</v>
       </c>
       <c r="I154" t="s">
         <v>274</v>
@@ -7161,14 +7540,14 @@
       <c r="L154" t="s">
         <v>266</v>
       </c>
-      <c r="M154" t="b">
-        <v>1</v>
+      <c r="M154" t="s">
+        <v>23</v>
       </c>
       <c r="N154" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O154" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.3">
@@ -7179,19 +7558,22 @@
         <v>264</v>
       </c>
       <c r="C155" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D155" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E155" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F155" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G155" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H155" t="s">
+        <v>21</v>
       </c>
       <c r="I155" t="s">
         <v>275</v>
@@ -7205,14 +7587,14 @@
       <c r="L155" t="s">
         <v>266</v>
       </c>
-      <c r="M155" t="b">
-        <v>1</v>
+      <c r="M155" t="s">
+        <v>23</v>
       </c>
       <c r="N155" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O155" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.3">
@@ -7223,19 +7605,22 @@
         <v>264</v>
       </c>
       <c r="C156" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D156" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E156" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F156" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G156" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H156" t="s">
+        <v>21</v>
       </c>
       <c r="I156" t="s">
         <v>276</v>
@@ -7249,14 +7634,14 @@
       <c r="L156" t="s">
         <v>266</v>
       </c>
-      <c r="M156" t="b">
-        <v>1</v>
+      <c r="M156" t="s">
+        <v>23</v>
       </c>
       <c r="N156" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O156" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.3">
@@ -7267,19 +7652,22 @@
         <v>264</v>
       </c>
       <c r="C157" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D157" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E157" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F157" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G157" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H157" t="s">
+        <v>21</v>
       </c>
       <c r="I157" t="s">
         <v>277</v>
@@ -7293,14 +7681,14 @@
       <c r="L157" t="s">
         <v>266</v>
       </c>
-      <c r="M157" t="b">
-        <v>1</v>
+      <c r="M157" t="s">
+        <v>23</v>
       </c>
       <c r="N157" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O157" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
@@ -7311,19 +7699,22 @@
         <v>264</v>
       </c>
       <c r="C158" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D158" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E158" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F158" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G158" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H158" t="s">
+        <v>21</v>
       </c>
       <c r="I158" t="s">
         <v>278</v>
@@ -7337,14 +7728,14 @@
       <c r="L158" t="s">
         <v>266</v>
       </c>
-      <c r="M158" t="b">
-        <v>1</v>
+      <c r="M158" t="s">
+        <v>23</v>
       </c>
       <c r="N158" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O158" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
@@ -7355,19 +7746,22 @@
         <v>264</v>
       </c>
       <c r="C159" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D159" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E159" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F159" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G159" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H159" t="s">
+        <v>21</v>
       </c>
       <c r="I159" t="s">
         <v>279</v>
@@ -7381,14 +7775,14 @@
       <c r="L159" t="s">
         <v>266</v>
       </c>
-      <c r="M159" t="b">
-        <v>1</v>
+      <c r="M159" t="s">
+        <v>23</v>
       </c>
       <c r="N159" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O159" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
@@ -7399,19 +7793,22 @@
         <v>264</v>
       </c>
       <c r="C160" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D160" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E160" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F160" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G160" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H160" t="s">
+        <v>21</v>
       </c>
       <c r="I160" t="s">
         <v>280</v>
@@ -7425,14 +7822,14 @@
       <c r="L160" t="s">
         <v>266</v>
       </c>
-      <c r="M160" t="b">
-        <v>1</v>
+      <c r="M160" t="s">
+        <v>23</v>
       </c>
       <c r="N160" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O160" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.3">
@@ -7443,13 +7840,16 @@
         <v>264</v>
       </c>
       <c r="C161" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E161" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G161" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H161" t="s">
+        <v>21</v>
       </c>
       <c r="I161" t="s">
         <v>281</v>
@@ -7463,8 +7863,8 @@
       <c r="L161" t="s">
         <v>266</v>
       </c>
-      <c r="M161" t="b">
-        <v>1</v>
+      <c r="M161" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.3">
@@ -7478,13 +7878,16 @@
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E162" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G162" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H162" t="s">
+        <v>21</v>
       </c>
       <c r="I162" t="s">
         <v>284</v>
@@ -7496,10 +7899,10 @@
         <v>0</v>
       </c>
       <c r="L162" t="s">
-        <v>28</v>
-      </c>
-      <c r="M162" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M162" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.3">
@@ -7510,18 +7913,21 @@
         <v>283</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D163" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E163" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G163" t="s">
         <v>19</v>
       </c>
       <c r="H163" t="s">
+        <v>22</v>
+      </c>
+      <c r="I163" t="s">
         <v>21</v>
       </c>
       <c r="J163">
@@ -7531,10 +7937,10 @@
         <v>0</v>
       </c>
       <c r="L163" t="s">
-        <v>28</v>
-      </c>
-      <c r="M163" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M163" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.3">
@@ -7545,13 +7951,13 @@
         <v>283</v>
       </c>
       <c r="C164" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D164" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E164" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G164" t="s">
         <v>19</v>
@@ -7559,6 +7965,9 @@
       <c r="H164" t="s">
         <v>285</v>
       </c>
+      <c r="I164" t="s">
+        <v>21</v>
+      </c>
       <c r="J164">
         <v>80</v>
       </c>
@@ -7566,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="L164" t="s">
-        <v>28</v>
-      </c>
-      <c r="M164" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M164" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.3">
@@ -7580,13 +7989,13 @@
         <v>283</v>
       </c>
       <c r="C165" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D165" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E165" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G165" t="s">
         <v>19</v>
@@ -7594,6 +8003,9 @@
       <c r="H165" t="s">
         <v>269</v>
       </c>
+      <c r="I165" t="s">
+        <v>21</v>
+      </c>
       <c r="J165">
         <v>80</v>
       </c>
@@ -7601,10 +8013,10 @@
         <v>0</v>
       </c>
       <c r="L165" t="s">
-        <v>28</v>
-      </c>
-      <c r="M165" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M165" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.3">
@@ -7615,19 +8027,22 @@
         <v>283</v>
       </c>
       <c r="C166" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D166" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E166" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F166" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G166" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H166" t="s">
+        <v>21</v>
       </c>
       <c r="I166" t="s">
         <v>286</v>
@@ -7639,16 +8054,16 @@
         <v>2</v>
       </c>
       <c r="L166" t="s">
-        <v>28</v>
-      </c>
-      <c r="M166" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M166" t="s">
+        <v>23</v>
       </c>
       <c r="N166" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O166" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
@@ -7659,19 +8074,22 @@
         <v>283</v>
       </c>
       <c r="C167" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D167" t="s">
+        <v>216</v>
+      </c>
+      <c r="E167" t="s">
+        <v>76</v>
+      </c>
+      <c r="F167" t="s">
         <v>214</v>
       </c>
-      <c r="E167" t="s">
-        <v>74</v>
-      </c>
-      <c r="F167" t="s">
-        <v>212</v>
-      </c>
       <c r="G167" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H167" t="s">
+        <v>21</v>
       </c>
       <c r="I167" t="s">
         <v>287</v>
@@ -7683,16 +8101,16 @@
         <v>0</v>
       </c>
       <c r="L167" t="s">
-        <v>28</v>
-      </c>
-      <c r="M167" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M167" t="s">
+        <v>23</v>
       </c>
       <c r="N167" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O167" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.3">
@@ -7703,19 +8121,22 @@
         <v>283</v>
       </c>
       <c r="C168" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D168" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E168" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F168" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G168" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H168" t="s">
+        <v>21</v>
       </c>
       <c r="I168" t="s">
         <v>288</v>
@@ -7727,16 +8148,16 @@
         <v>16</v>
       </c>
       <c r="L168" t="s">
-        <v>28</v>
-      </c>
-      <c r="M168" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M168" t="s">
+        <v>23</v>
       </c>
       <c r="N168" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O168" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.3">
@@ -7747,19 +8168,22 @@
         <v>283</v>
       </c>
       <c r="C169" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D169" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E169" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F169" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G169" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H169" t="s">
+        <v>21</v>
       </c>
       <c r="I169" t="s">
         <v>289</v>
@@ -7771,16 +8195,16 @@
         <v>29</v>
       </c>
       <c r="L169" t="s">
-        <v>28</v>
-      </c>
-      <c r="M169" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M169" t="s">
+        <v>290</v>
       </c>
       <c r="N169" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O169" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.3">
@@ -7791,22 +8215,25 @@
         <v>283</v>
       </c>
       <c r="C170" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D170" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E170" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F170" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G170" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H170" t="s">
+        <v>21</v>
       </c>
       <c r="I170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J170">
         <v>66</v>
@@ -7815,16 +8242,16 @@
         <v>14</v>
       </c>
       <c r="L170" t="s">
-        <v>28</v>
-      </c>
-      <c r="M170" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M170" t="s">
+        <v>23</v>
       </c>
       <c r="N170" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O170" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.3">
@@ -7835,22 +8262,25 @@
         <v>283</v>
       </c>
       <c r="C171" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D171" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E171" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F171" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G171" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H171" t="s">
+        <v>21</v>
       </c>
       <c r="I171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J171">
         <v>58</v>
@@ -7859,16 +8289,16 @@
         <v>22</v>
       </c>
       <c r="L171" t="s">
-        <v>28</v>
-      </c>
-      <c r="M171" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M171" t="s">
+        <v>23</v>
       </c>
       <c r="N171" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O171" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.3">
@@ -7879,22 +8309,25 @@
         <v>283</v>
       </c>
       <c r="C172" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D172" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E172" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F172" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G172" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H172" t="s">
+        <v>21</v>
       </c>
       <c r="I172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J172">
         <v>78</v>
@@ -7903,16 +8336,16 @@
         <v>2</v>
       </c>
       <c r="L172" t="s">
-        <v>28</v>
-      </c>
-      <c r="M172" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M172" t="s">
+        <v>23</v>
       </c>
       <c r="N172" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O172" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.3">
@@ -7923,22 +8356,25 @@
         <v>283</v>
       </c>
       <c r="C173" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D173" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E173" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F173" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G173" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H173" t="s">
+        <v>21</v>
       </c>
       <c r="I173" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J173">
         <v>64</v>
@@ -7947,16 +8383,16 @@
         <v>16</v>
       </c>
       <c r="L173" t="s">
-        <v>28</v>
-      </c>
-      <c r="M173" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M173" t="s">
+        <v>23</v>
       </c>
       <c r="N173" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O173" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.3">
@@ -7967,22 +8403,25 @@
         <v>283</v>
       </c>
       <c r="C174" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D174" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E174" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F174" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G174" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H174" t="s">
+        <v>21</v>
       </c>
       <c r="I174" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J174">
         <v>51</v>
@@ -7991,16 +8430,16 @@
         <v>29</v>
       </c>
       <c r="L174" t="s">
-        <v>28</v>
-      </c>
-      <c r="M174" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M174" t="s">
+        <v>290</v>
       </c>
       <c r="N174" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O174" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.3">
@@ -8011,22 +8450,25 @@
         <v>283</v>
       </c>
       <c r="C175" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D175" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E175" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F175" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G175" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H175" t="s">
+        <v>21</v>
       </c>
       <c r="I175" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J175">
         <v>66</v>
@@ -8035,16 +8477,16 @@
         <v>14</v>
       </c>
       <c r="L175" t="s">
-        <v>28</v>
-      </c>
-      <c r="M175" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M175" t="s">
+        <v>23</v>
       </c>
       <c r="N175" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.3">
@@ -8055,22 +8497,25 @@
         <v>283</v>
       </c>
       <c r="C176" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D176" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E176" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F176" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G176" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H176" t="s">
+        <v>21</v>
       </c>
       <c r="I176" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J176">
         <v>58</v>
@@ -8079,16 +8524,16 @@
         <v>22</v>
       </c>
       <c r="L176" t="s">
-        <v>28</v>
-      </c>
-      <c r="M176" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M176" t="s">
+        <v>23</v>
       </c>
       <c r="N176" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O176" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.3">
@@ -8099,19 +8544,19 @@
         <v>283</v>
       </c>
       <c r="C177" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E177" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G177" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H177" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I177" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J177">
         <v>80</v>
@@ -8120,33 +8565,36 @@
         <v>0</v>
       </c>
       <c r="L177" t="s">
-        <v>28</v>
-      </c>
-      <c r="M177" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="M177" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C178" t="s">
         <v>17</v>
       </c>
       <c r="D178" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E178" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G178" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H178" t="s">
+        <v>21</v>
       </c>
       <c r="I178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J178">
         <v>4069</v>
@@ -8155,33 +8603,36 @@
         <v>0</v>
       </c>
       <c r="L178" t="s">
-        <v>206</v>
-      </c>
-      <c r="M178" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M178" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B179" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C179" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D179" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E179" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G179" t="s">
         <v>19</v>
       </c>
       <c r="H179" t="s">
-        <v>302</v>
+        <v>303</v>
+      </c>
+      <c r="I179" t="s">
+        <v>21</v>
       </c>
       <c r="J179">
         <v>4069</v>
@@ -8190,27 +8641,27 @@
         <v>0</v>
       </c>
       <c r="L179" t="s">
-        <v>206</v>
-      </c>
-      <c r="M179" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M179" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B180" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C180" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D180" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E180" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G180" t="s">
         <v>19</v>
@@ -8218,6 +8669,9 @@
       <c r="H180" t="s">
         <v>269</v>
       </c>
+      <c r="I180" t="s">
+        <v>21</v>
+      </c>
       <c r="J180">
         <v>4069</v>
       </c>
@@ -8225,36 +8679,39 @@
         <v>0</v>
       </c>
       <c r="L180" t="s">
-        <v>206</v>
-      </c>
-      <c r="M180" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M180" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B181" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C181" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D181" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E181" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F181" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G181" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H181" t="s">
+        <v>21</v>
       </c>
       <c r="I181" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J181">
         <v>4069</v>
@@ -8263,42 +8720,45 @@
         <v>0</v>
       </c>
       <c r="L181" t="s">
-        <v>206</v>
-      </c>
-      <c r="M181" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M181" t="s">
+        <v>23</v>
       </c>
       <c r="N181" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O181" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B182" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C182" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D182" t="s">
+        <v>216</v>
+      </c>
+      <c r="E182" t="s">
+        <v>76</v>
+      </c>
+      <c r="F182" t="s">
         <v>214</v>
       </c>
-      <c r="E182" t="s">
-        <v>74</v>
-      </c>
-      <c r="F182" t="s">
-        <v>212</v>
-      </c>
       <c r="G182" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H182" t="s">
+        <v>21</v>
       </c>
       <c r="I182" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J182">
         <v>4069</v>
@@ -8307,42 +8767,45 @@
         <v>0</v>
       </c>
       <c r="L182" t="s">
-        <v>206</v>
-      </c>
-      <c r="M182" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M182" t="s">
+        <v>23</v>
       </c>
       <c r="N182" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O182" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B183" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C183" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D183" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E183" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F183" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G183" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H183" t="s">
+        <v>21</v>
       </c>
       <c r="I183" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J183">
         <v>4069</v>
@@ -8351,42 +8814,45 @@
         <v>0</v>
       </c>
       <c r="L183" t="s">
-        <v>206</v>
-      </c>
-      <c r="M183" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M183" t="s">
+        <v>23</v>
       </c>
       <c r="N183" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O183" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B184" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C184" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D184" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E184" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F184" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G184" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H184" t="s">
+        <v>21</v>
       </c>
       <c r="I184" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J184">
         <v>4068</v>
@@ -8395,42 +8861,45 @@
         <v>1</v>
       </c>
       <c r="L184" t="s">
-        <v>206</v>
-      </c>
-      <c r="M184" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M184" t="s">
+        <v>23</v>
       </c>
       <c r="N184" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O184" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B185" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C185" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D185" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E185" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F185" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G185" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H185" t="s">
+        <v>21</v>
       </c>
       <c r="I185" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J185">
         <v>4069</v>
@@ -8439,42 +8908,45 @@
         <v>0</v>
       </c>
       <c r="L185" t="s">
-        <v>206</v>
-      </c>
-      <c r="M185" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M185" t="s">
+        <v>23</v>
       </c>
       <c r="N185" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O185" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B186" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C186" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D186" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E186" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F186" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G186" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H186" t="s">
+        <v>21</v>
       </c>
       <c r="I186" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J186">
         <v>4069</v>
@@ -8483,42 +8955,45 @@
         <v>0</v>
       </c>
       <c r="L186" t="s">
-        <v>206</v>
-      </c>
-      <c r="M186" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M186" t="s">
+        <v>23</v>
       </c>
       <c r="N186" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O186" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B187" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C187" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D187" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E187" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F187" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G187" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H187" t="s">
+        <v>21</v>
       </c>
       <c r="I187" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J187">
         <v>4069</v>
@@ -8527,42 +9002,45 @@
         <v>0</v>
       </c>
       <c r="L187" t="s">
-        <v>206</v>
-      </c>
-      <c r="M187" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M187" t="s">
+        <v>23</v>
       </c>
       <c r="N187" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O187" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B188" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C188" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D188" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E188" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F188" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G188" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H188" t="s">
+        <v>21</v>
       </c>
       <c r="I188" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J188">
         <v>4069</v>
@@ -8571,42 +9049,45 @@
         <v>0</v>
       </c>
       <c r="L188" t="s">
-        <v>206</v>
-      </c>
-      <c r="M188" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M188" t="s">
+        <v>23</v>
       </c>
       <c r="N188" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O188" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B189" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C189" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D189" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E189" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F189" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G189" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H189" t="s">
+        <v>21</v>
       </c>
       <c r="I189" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J189">
         <v>4069</v>
@@ -8615,42 +9096,45 @@
         <v>0</v>
       </c>
       <c r="L189" t="s">
-        <v>206</v>
-      </c>
-      <c r="M189" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M189" t="s">
+        <v>23</v>
       </c>
       <c r="N189" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O189" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B190" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C190" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D190" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E190" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F190" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G190" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H190" t="s">
+        <v>21</v>
       </c>
       <c r="I190" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J190">
         <v>4069</v>
@@ -8659,42 +9143,45 @@
         <v>0</v>
       </c>
       <c r="L190" t="s">
-        <v>206</v>
-      </c>
-      <c r="M190" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M190" t="s">
+        <v>23</v>
       </c>
       <c r="N190" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O190" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B191" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C191" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D191" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E191" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F191" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G191" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="H191" t="s">
+        <v>21</v>
       </c>
       <c r="I191" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J191">
         <v>4068</v>
@@ -8703,36 +9190,39 @@
         <v>1</v>
       </c>
       <c r="L191" t="s">
-        <v>206</v>
-      </c>
-      <c r="M191" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M191" t="s">
+        <v>23</v>
       </c>
       <c r="N191" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O191" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B192" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C192" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E192" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G192" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H192" t="s">
+        <v>21</v>
       </c>
       <c r="I192" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J192">
         <v>4069</v>
@@ -8741,10 +9231,10 @@
         <v>0</v>
       </c>
       <c r="L192" t="s">
-        <v>206</v>
-      </c>
-      <c r="M192" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="M192" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/WP-2/Data_cleaning/ADNI_variables_cleaned2.xlsx
+++ b/WP-2/Data_cleaning/ADNI_variables_cleaned2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/chiara_pollicini_ifabfoundation_org/Documents/Documenti/Github/AIND/WP-2/Data_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_26B1E901577FF60F62355476585DCE3A8745FCA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E61BBE60-48F1-479E-9C64-AD97D5F3A772}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_35C5B15190482E0E62355476585DCE3A8745CC20" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C93FF2F7-B0E1-45F4-A1BA-17B25A228C51}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-3705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="316">
   <si>
     <t>file_name</t>
   </si>
@@ -136,21 +136,21 @@
     <t>97.8, 55.0</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>PTEDUCAT</t>
+  </si>
+  <si>
+    <t>EDUCAT</t>
+  </si>
+  <si>
+    <t>20.0, 4.0</t>
+  </si>
+  <si>
     <t>cofattore</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>PTEDUCAT</t>
-  </si>
-  <si>
-    <t>EDUCAT</t>
-  </si>
-  <si>
-    <t>20.0, 4.0</t>
-  </si>
-  <si>
     <t>APOE</t>
   </si>
   <si>
@@ -163,235 +163,235 @@
     <t>2.0, 0.0</t>
   </si>
   <si>
+    <t>CDR</t>
+  </si>
+  <si>
+    <t>CDRSB</t>
+  </si>
+  <si>
+    <t>18.0, 0.0</t>
+  </si>
+  <si>
     <t>predittore</t>
   </si>
   <si>
+    <t>scala</t>
+  </si>
+  <si>
+    <t>ADAS</t>
+  </si>
+  <si>
+    <t>ADAS11</t>
+  </si>
+  <si>
+    <t>70.0, 0.0</t>
+  </si>
+  <si>
+    <t>ADAS13</t>
+  </si>
+  <si>
+    <t>85.0, 0.0</t>
+  </si>
+  <si>
+    <t>MMSE</t>
+  </si>
+  <si>
+    <t>30.0, 0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAVLT </t>
+  </si>
+  <si>
+    <t>RAVLT_immediate</t>
+  </si>
+  <si>
+    <t>75.0, 0.0</t>
+  </si>
+  <si>
+    <t>FAQ</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Ventricles</t>
+  </si>
+  <si>
+    <t>162729.0, 5650.0</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>Hippocampus</t>
+  </si>
+  <si>
+    <t>11207.0, 2219.0</t>
+  </si>
+  <si>
+    <t>Entorhinal</t>
+  </si>
+  <si>
+    <t>7062.0, 976.0</t>
+  </si>
+  <si>
+    <t>Fusiform</t>
+  </si>
+  <si>
+    <t>29950.0, 7739.0</t>
+  </si>
+  <si>
+    <t>MidTemp</t>
+  </si>
+  <si>
+    <t>32324.0, 8044.0</t>
+  </si>
+  <si>
+    <t>ICV</t>
+  </si>
+  <si>
+    <t>3500150.0, 716133.0</t>
+  </si>
+  <si>
+    <t>AGE_bl</t>
+  </si>
+  <si>
+    <t>91.4, 55.0</t>
+  </si>
+  <si>
+    <t>Visit</t>
+  </si>
+  <si>
+    <t>VISIT_MONTH</t>
+  </si>
+  <si>
+    <t>204.0, 0.0</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>['PTGENDER']</t>
+  </si>
+  <si>
+    <t>GENDER/female</t>
+  </si>
+  <si>
+    <t>&lt;class 'numpy.bool'&gt;</t>
+  </si>
+  <si>
+    <t>False, True</t>
+  </si>
+  <si>
+    <t>GENDER/male</t>
+  </si>
+  <si>
+    <t>True, False</t>
+  </si>
+  <si>
+    <t>Marry</t>
+  </si>
+  <si>
+    <t>['PTMARRY']</t>
+  </si>
+  <si>
+    <t>MARRY/divorced</t>
+  </si>
+  <si>
+    <t>MARRY/married</t>
+  </si>
+  <si>
+    <t>MARRY/single</t>
+  </si>
+  <si>
+    <t>MARRY/widowed</t>
+  </si>
+  <si>
+    <t>Ethnicity</t>
+  </si>
+  <si>
+    <t>['PTETHCAT']</t>
+  </si>
+  <si>
+    <t>ETHNICITY/latino</t>
+  </si>
+  <si>
+    <t>ETHNICITY/not_latino</t>
+  </si>
+  <si>
+    <t>['PTRACCAT']</t>
+  </si>
+  <si>
+    <t>RACE/Asian</t>
+  </si>
+  <si>
+    <t>RACE/Black</t>
+  </si>
+  <si>
+    <t>RACE/Mixed</t>
+  </si>
+  <si>
+    <t>RACE/Native_american</t>
+  </si>
+  <si>
+    <t>RACE/White</t>
+  </si>
+  <si>
+    <t>Diagnosi</t>
+  </si>
+  <si>
+    <t>['DX']</t>
+  </si>
+  <si>
+    <t>DX/CN</t>
+  </si>
+  <si>
+    <t>DX/Dementia</t>
+  </si>
+  <si>
+    <t>DX/MCI</t>
+  </si>
+  <si>
+    <t>ADSP Phenotype Harmonization Consortium (PHC) - Composite Biomarker Scores</t>
+  </si>
+  <si>
+    <t>ADSP_PHC_BIOMARKER</t>
+  </si>
+  <si>
+    <t>011_S_0003, 022_S_0004, 011_S_0005, 011_S_0008, 011_S_0010</t>
+  </si>
+  <si>
+    <t>ADNI3, ADNI4</t>
+  </si>
+  <si>
+    <t>5296.0, 3.0</t>
+  </si>
+  <si>
+    <t>PHASE</t>
+  </si>
+  <si>
+    <t>ADNI1, ADNIGO, ADNI2</t>
+  </si>
+  <si>
+    <t>DRAWDATE</t>
+  </si>
+  <si>
+    <t>2006-09-13, 2006-11-28, 2006-09-06, 2006-09-20, 2006-11-10</t>
+  </si>
+  <si>
+    <t>PHC_Education</t>
+  </si>
+  <si>
+    <t>Tau</t>
+  </si>
+  <si>
+    <t>PHC_Tau</t>
+  </si>
+  <si>
+    <t>2.66834693328626, -2.75390285653023</t>
+  </si>
+  <si>
     <t>intervallo</t>
-  </si>
-  <si>
-    <t>CDR</t>
-  </si>
-  <si>
-    <t>CDRSB</t>
-  </si>
-  <si>
-    <t>18.0, 0.0</t>
-  </si>
-  <si>
-    <t>scala</t>
-  </si>
-  <si>
-    <t>ADAS</t>
-  </si>
-  <si>
-    <t>ADAS11</t>
-  </si>
-  <si>
-    <t>70.0, 0.0</t>
-  </si>
-  <si>
-    <t>ADAS13</t>
-  </si>
-  <si>
-    <t>85.0, 0.0</t>
-  </si>
-  <si>
-    <t>MMSE</t>
-  </si>
-  <si>
-    <t>30.0, 0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAVLT </t>
-  </si>
-  <si>
-    <t>RAVLT_immediate</t>
-  </si>
-  <si>
-    <t>75.0, 0.0</t>
-  </si>
-  <si>
-    <t>FAQ</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Ventricles</t>
-  </si>
-  <si>
-    <t>162729.0, 5650.0</t>
-  </si>
-  <si>
-    <t>volume</t>
-  </si>
-  <si>
-    <t>Hippocampus</t>
-  </si>
-  <si>
-    <t>11207.0, 2219.0</t>
-  </si>
-  <si>
-    <t>Entorhinal</t>
-  </si>
-  <si>
-    <t>7062.0, 976.0</t>
-  </si>
-  <si>
-    <t>Fusiform</t>
-  </si>
-  <si>
-    <t>29950.0, 7739.0</t>
-  </si>
-  <si>
-    <t>MidTemp</t>
-  </si>
-  <si>
-    <t>32324.0, 8044.0</t>
-  </si>
-  <si>
-    <t>ICV</t>
-  </si>
-  <si>
-    <t>3500150.0, 716133.0</t>
-  </si>
-  <si>
-    <t>AGE_bl</t>
-  </si>
-  <si>
-    <t>91.4, 55.0</t>
-  </si>
-  <si>
-    <t>Visit</t>
-  </si>
-  <si>
-    <t>VISIT_MONTH</t>
-  </si>
-  <si>
-    <t>204.0, 0.0</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>['PTGENDER']</t>
-  </si>
-  <si>
-    <t>GENDER/female</t>
-  </si>
-  <si>
-    <t>&lt;class 'numpy.bool'&gt;</t>
-  </si>
-  <si>
-    <t>False, True</t>
-  </si>
-  <si>
-    <t>GENDER/male</t>
-  </si>
-  <si>
-    <t>True, False</t>
-  </si>
-  <si>
-    <t>Marry</t>
-  </si>
-  <si>
-    <t>['PTMARRY']</t>
-  </si>
-  <si>
-    <t>MARRY/divorced</t>
-  </si>
-  <si>
-    <t>MARRY/married</t>
-  </si>
-  <si>
-    <t>MARRY/single</t>
-  </si>
-  <si>
-    <t>MARRY/widowed</t>
-  </si>
-  <si>
-    <t>Ethnicity</t>
-  </si>
-  <si>
-    <t>['PTETHCAT']</t>
-  </si>
-  <si>
-    <t>ETHNICITY/latino</t>
-  </si>
-  <si>
-    <t>ETHNICITY/not_latino</t>
-  </si>
-  <si>
-    <t>['PTRACCAT']</t>
-  </si>
-  <si>
-    <t>RACE/Asian</t>
-  </si>
-  <si>
-    <t>RACE/Black</t>
-  </si>
-  <si>
-    <t>RACE/Mixed</t>
-  </si>
-  <si>
-    <t>RACE/Native_american</t>
-  </si>
-  <si>
-    <t>RACE/White</t>
-  </si>
-  <si>
-    <t>Diagnosi</t>
-  </si>
-  <si>
-    <t>['DX']</t>
-  </si>
-  <si>
-    <t>DX/CN</t>
-  </si>
-  <si>
-    <t>DX/Dementia</t>
-  </si>
-  <si>
-    <t>DX/MCI</t>
-  </si>
-  <si>
-    <t>ADSP Phenotype Harmonization Consortium (PHC) - Composite Biomarker Scores</t>
-  </si>
-  <si>
-    <t>ADSP_PHC_BIOMARKER</t>
-  </si>
-  <si>
-    <t>011_S_0003, 022_S_0004, 011_S_0005, 011_S_0008, 011_S_0010</t>
-  </si>
-  <si>
-    <t>ADNI3, ADNI4</t>
-  </si>
-  <si>
-    <t>5296.0, 3.0</t>
-  </si>
-  <si>
-    <t>PHASE</t>
-  </si>
-  <si>
-    <t>ADNI1, ADNIGO, ADNI2</t>
-  </si>
-  <si>
-    <t>DRAWDATE</t>
-  </si>
-  <si>
-    <t>2006-09-13, 2006-11-28, 2006-09-06, 2006-09-20, 2006-11-10</t>
-  </si>
-  <si>
-    <t>PHC_Education</t>
-  </si>
-  <si>
-    <t>Tau</t>
-  </si>
-  <si>
-    <t>PHC_Tau</t>
-  </si>
-  <si>
-    <t>2.66834693328626, -2.75390285653023</t>
   </si>
   <si>
     <t>PHC_Visit</t>
@@ -986,7 +986,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1024,10 +1023,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1337,9 +1342,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O192"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.33203125" style="3" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1392,7 +1400,7 @@
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
@@ -1430,7 +1438,7 @@
       <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D3" t="s">
@@ -1468,7 +1476,7 @@
       <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
@@ -1506,7 +1514,7 @@
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D5" t="s">
@@ -1544,7 +1552,7 @@
       <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
@@ -1573,9 +1581,6 @@
       </c>
       <c r="M6" t="s">
         <v>23</v>
-      </c>
-      <c r="N6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -1585,14 +1590,14 @@
       <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>41</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
@@ -1601,7 +1606,7 @@
         <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J7">
         <v>11135</v>
@@ -1616,7 +1621,7 @@
         <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -1626,7 +1631,7 @@
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D8" t="s">
@@ -1657,7 +1662,7 @@
         <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1667,14 +1672,14 @@
       <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
-        <v>49</v>
+      <c r="C9" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
         <v>36</v>
@@ -1683,7 +1688,7 @@
         <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J9">
         <v>10986</v>
@@ -1698,10 +1703,10 @@
         <v>23</v>
       </c>
       <c r="N9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -1711,14 +1716,14 @@
       <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
         <v>53</v>
       </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
         <v>36</v>
@@ -1727,7 +1732,7 @@
         <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J10">
         <v>11036</v>
@@ -1742,10 +1747,10 @@
         <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1755,14 +1760,14 @@
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" t="s">
-        <v>53</v>
+      <c r="C11" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
         <v>36</v>
@@ -1771,7 +1776,7 @@
         <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J11">
         <v>10937</v>
@@ -1786,10 +1791,10 @@
         <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1799,14 +1804,14 @@
       <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C12" t="s">
-        <v>58</v>
+      <c r="C12" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
@@ -1815,7 +1820,7 @@
         <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J12">
         <v>11067</v>
@@ -1830,10 +1835,10 @@
         <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -1843,14 +1848,14 @@
       <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="D13" t="s">
-        <v>61</v>
-      </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
         <v>36</v>
@@ -1859,7 +1864,7 @@
         <v>21</v>
       </c>
       <c r="I13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J13">
         <v>10951</v>
@@ -1874,10 +1879,10 @@
         <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1887,14 +1892,14 @@
       <c r="B14" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>63</v>
+      <c r="C14" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
         <v>36</v>
@@ -1903,7 +1908,7 @@
         <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J14">
         <v>10975</v>
@@ -1918,10 +1923,10 @@
         <v>23</v>
       </c>
       <c r="N14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -1931,14 +1936,14 @@
       <c r="B15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="s">
         <v>64</v>
       </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
         <v>36</v>
@@ -1947,7 +1952,7 @@
         <v>21</v>
       </c>
       <c r="I15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J15">
         <v>8458</v>
@@ -1962,10 +1967,10 @@
         <v>23</v>
       </c>
       <c r="N15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1975,14 +1980,14 @@
       <c r="B16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" t="s">
-        <v>64</v>
+      <c r="C16" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G16" t="s">
         <v>36</v>
@@ -1991,7 +1996,7 @@
         <v>21</v>
       </c>
       <c r="I16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J16">
         <v>7874</v>
@@ -2006,10 +2011,10 @@
         <v>23</v>
       </c>
       <c r="N16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -2019,14 +2024,14 @@
       <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" t="s">
-        <v>64</v>
+      <c r="C17" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
         <v>36</v>
@@ -2035,7 +2040,7 @@
         <v>21</v>
       </c>
       <c r="I17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J17">
         <v>7488</v>
@@ -2050,10 +2055,10 @@
         <v>23</v>
       </c>
       <c r="N17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -2063,14 +2068,14 @@
       <c r="B18" t="s">
         <v>16</v>
       </c>
-      <c r="C18" t="s">
-        <v>64</v>
+      <c r="C18" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G18" t="s">
         <v>36</v>
@@ -2079,7 +2084,7 @@
         <v>21</v>
       </c>
       <c r="I18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J18">
         <v>7488</v>
@@ -2094,10 +2099,10 @@
         <v>23</v>
       </c>
       <c r="N18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -2107,14 +2112,14 @@
       <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" t="s">
-        <v>64</v>
+      <c r="C19" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s">
         <v>36</v>
@@ -2123,7 +2128,7 @@
         <v>21</v>
       </c>
       <c r="I19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J19">
         <v>7488</v>
@@ -2137,8 +2142,11 @@
       <c r="M19" t="s">
         <v>23</v>
       </c>
+      <c r="N19" t="s">
+        <v>50</v>
+      </c>
       <c r="O19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -2148,14 +2156,14 @@
       <c r="B20" t="s">
         <v>16</v>
       </c>
-      <c r="C20" t="s">
-        <v>64</v>
+      <c r="C20" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
         <v>36</v>
@@ -2164,7 +2172,7 @@
         <v>21</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J20">
         <v>9023</v>
@@ -2177,6 +2185,12 @@
       </c>
       <c r="M20" t="s">
         <v>23</v>
+      </c>
+      <c r="N20" t="s">
+        <v>50</v>
+      </c>
+      <c r="O20" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -2186,14 +2200,14 @@
       <c r="B21" t="s">
         <v>16</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D21" t="s">
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s">
         <v>36</v>
@@ -2202,7 +2216,7 @@
         <v>21</v>
       </c>
       <c r="I21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J21">
         <v>11129</v>
@@ -2224,14 +2238,14 @@
       <c r="B22" t="s">
         <v>16</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
         <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" t="s">
-        <v>81</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
@@ -2240,7 +2254,7 @@
         <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J22">
         <v>11135</v>
@@ -2262,20 +2276,20 @@
       <c r="B23" t="s">
         <v>16</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
         <v>83</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>84</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>85</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>86</v>
-      </c>
-      <c r="H23" t="s">
-        <v>87</v>
       </c>
       <c r="I23" t="s">
         <v>21</v>
@@ -2293,7 +2307,7 @@
         <v>23</v>
       </c>
       <c r="N23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -2303,20 +2317,20 @@
       <c r="B24" t="s">
         <v>16</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" t="s">
         <v>83</v>
       </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
       <c r="E24" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" t="s">
         <v>88</v>
-      </c>
-      <c r="G24" t="s">
-        <v>86</v>
-      </c>
-      <c r="H24" t="s">
-        <v>89</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -2334,7 +2348,7 @@
         <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -2344,20 +2358,20 @@
       <c r="B25" t="s">
         <v>16</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" t="s">
         <v>90</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>91</v>
       </c>
-      <c r="E25" t="s">
-        <v>92</v>
-      </c>
       <c r="G25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" t="s">
         <v>86</v>
-      </c>
-      <c r="H25" t="s">
-        <v>87</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -2375,7 +2389,7 @@
         <v>23</v>
       </c>
       <c r="N25" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -2385,20 +2399,20 @@
       <c r="B26" t="s">
         <v>16</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" t="s">
         <v>90</v>
       </c>
-      <c r="D26" t="s">
-        <v>91</v>
-      </c>
       <c r="E26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s">
         <v>21</v>
@@ -2416,7 +2430,7 @@
         <v>23</v>
       </c>
       <c r="N26" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
@@ -2426,20 +2440,20 @@
       <c r="B27" t="s">
         <v>16</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" t="s">
         <v>90</v>
       </c>
-      <c r="D27" t="s">
-        <v>91</v>
-      </c>
       <c r="E27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" t="s">
         <v>86</v>
-      </c>
-      <c r="H27" t="s">
-        <v>87</v>
       </c>
       <c r="I27" t="s">
         <v>21</v>
@@ -2457,7 +2471,7 @@
         <v>23</v>
       </c>
       <c r="N27" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -2467,20 +2481,20 @@
       <c r="B28" t="s">
         <v>16</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" t="s">
         <v>90</v>
       </c>
-      <c r="D28" t="s">
-        <v>91</v>
-      </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" t="s">
         <v>86</v>
-      </c>
-      <c r="H28" t="s">
-        <v>87</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -2498,7 +2512,7 @@
         <v>23</v>
       </c>
       <c r="N28" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -2508,20 +2522,20 @@
       <c r="B29" t="s">
         <v>16</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" t="s">
         <v>96</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>97</v>
       </c>
-      <c r="E29" t="s">
-        <v>98</v>
-      </c>
       <c r="G29" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" t="s">
         <v>86</v>
-      </c>
-      <c r="H29" t="s">
-        <v>87</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -2539,7 +2553,7 @@
         <v>23</v>
       </c>
       <c r="N29" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -2549,20 +2563,20 @@
       <c r="B30" t="s">
         <v>16</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" t="s">
         <v>96</v>
       </c>
-      <c r="D30" t="s">
-        <v>97</v>
-      </c>
       <c r="E30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s">
         <v>21</v>
@@ -2580,7 +2594,7 @@
         <v>23</v>
       </c>
       <c r="N30" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -2590,20 +2604,20 @@
       <c r="B31" t="s">
         <v>16</v>
       </c>
-      <c r="C31" t="s">
-        <v>96</v>
+      <c r="C31" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D31" t="s">
+        <v>99</v>
+      </c>
+      <c r="E31" t="s">
         <v>100</v>
       </c>
-      <c r="E31" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" t="s">
+        <v>85</v>
+      </c>
+      <c r="H31" t="s">
         <v>86</v>
-      </c>
-      <c r="H31" t="s">
-        <v>87</v>
       </c>
       <c r="I31" t="s">
         <v>21</v>
@@ -2621,7 +2635,7 @@
         <v>23</v>
       </c>
       <c r="N31" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -2631,20 +2645,20 @@
       <c r="B32" t="s">
         <v>16</v>
       </c>
-      <c r="C32" t="s">
-        <v>96</v>
+      <c r="C32" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G32" t="s">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s">
         <v>86</v>
-      </c>
-      <c r="H32" t="s">
-        <v>87</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -2662,7 +2676,7 @@
         <v>23</v>
       </c>
       <c r="N32" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
@@ -2672,20 +2686,20 @@
       <c r="B33" t="s">
         <v>16</v>
       </c>
-      <c r="C33" t="s">
-        <v>96</v>
+      <c r="C33" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G33" t="s">
+        <v>85</v>
+      </c>
+      <c r="H33" t="s">
         <v>86</v>
-      </c>
-      <c r="H33" t="s">
-        <v>87</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -2703,7 +2717,7 @@
         <v>23</v>
       </c>
       <c r="N33" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
@@ -2713,20 +2727,20 @@
       <c r="B34" t="s">
         <v>16</v>
       </c>
-      <c r="C34" t="s">
-        <v>96</v>
+      <c r="C34" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H34" t="s">
         <v>86</v>
-      </c>
-      <c r="H34" t="s">
-        <v>87</v>
       </c>
       <c r="I34" t="s">
         <v>21</v>
@@ -2744,7 +2758,7 @@
         <v>23</v>
       </c>
       <c r="N34" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
@@ -2754,20 +2768,20 @@
       <c r="B35" t="s">
         <v>16</v>
       </c>
-      <c r="C35" t="s">
-        <v>96</v>
+      <c r="C35" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s">
         <v>21</v>
@@ -2785,7 +2799,7 @@
         <v>23</v>
       </c>
       <c r="N35" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -2795,20 +2809,20 @@
       <c r="B36" t="s">
         <v>16</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" t="s">
         <v>106</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>107</v>
       </c>
-      <c r="E36" t="s">
-        <v>108</v>
-      </c>
       <c r="G36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I36" t="s">
         <v>21</v>
@@ -2833,20 +2847,20 @@
       <c r="B37" t="s">
         <v>16</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" t="s">
         <v>106</v>
       </c>
-      <c r="D37" t="s">
-        <v>107</v>
-      </c>
       <c r="E37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G37" t="s">
+        <v>85</v>
+      </c>
+      <c r="H37" t="s">
         <v>86</v>
-      </c>
-      <c r="H37" t="s">
-        <v>87</v>
       </c>
       <c r="I37" t="s">
         <v>21</v>
@@ -2871,20 +2885,20 @@
       <c r="B38" t="s">
         <v>16</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" t="s">
         <v>106</v>
       </c>
-      <c r="D38" t="s">
-        <v>107</v>
-      </c>
       <c r="E38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G38" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" t="s">
         <v>86</v>
-      </c>
-      <c r="H38" t="s">
-        <v>87</v>
       </c>
       <c r="I38" t="s">
         <v>21</v>
@@ -2904,12 +2918,12 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" t="s">
         <v>111</v>
       </c>
-      <c r="B39" t="s">
-        <v>112</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="C39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="s">
@@ -2922,7 +2936,7 @@
         <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I39" t="s">
         <v>21</v>
@@ -2934,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M39" t="s">
         <v>23</v>
@@ -2942,12 +2956,12 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" t="s">
         <v>111</v>
       </c>
-      <c r="B40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="C40" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
@@ -2963,7 +2977,7 @@
         <v>21</v>
       </c>
       <c r="I40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J40">
         <v>1245</v>
@@ -2972,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -2980,16 +2994,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" t="s">
         <v>111</v>
       </c>
-      <c r="B41" t="s">
-        <v>112</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="C41" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E41" t="s">
         <v>29</v>
@@ -2998,7 +3012,7 @@
         <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I41" t="s">
         <v>21</v>
@@ -3010,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M41" t="s">
         <v>23</v>
@@ -3018,16 +3032,16 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" t="s">
         <v>111</v>
       </c>
-      <c r="B42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" t="s">
-        <v>80</v>
+      <c r="C42" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E42" t="s">
         <v>32</v>
@@ -3036,7 +3050,7 @@
         <v>19</v>
       </c>
       <c r="H42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I42" t="s">
         <v>21</v>
@@ -3048,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M42" t="s">
         <v>23</v>
@@ -3056,19 +3070,19 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" t="s">
         <v>111</v>
       </c>
-      <c r="B43" t="s">
-        <v>112</v>
-      </c>
-      <c r="C43" t="s">
-        <v>39</v>
+      <c r="C43" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="D43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G43" t="s">
         <v>25</v>
@@ -3077,7 +3091,7 @@
         <v>21</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J43">
         <v>1245</v>
@@ -3086,30 +3100,30 @@
         <v>0</v>
       </c>
       <c r="L43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M43" t="s">
         <v>23</v>
       </c>
       <c r="N43" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" t="s">
         <v>111</v>
       </c>
-      <c r="B44" t="s">
-        <v>112</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="C44" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" t="s">
         <v>121</v>
       </c>
-      <c r="D44" t="s">
-        <v>122</v>
-      </c>
       <c r="E44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G44" t="s">
         <v>36</v>
@@ -3118,7 +3132,7 @@
         <v>21</v>
       </c>
       <c r="I44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J44">
         <v>1212</v>
@@ -3127,27 +3141,27 @@
         <v>33</v>
       </c>
       <c r="L44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M44" t="s">
         <v>23</v>
       </c>
       <c r="N44" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O44" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" t="s">
         <v>111</v>
       </c>
-      <c r="B45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" t="s">
-        <v>80</v>
+      <c r="C45" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D45" t="s">
         <v>124</v>
@@ -3171,7 +3185,7 @@
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M45" t="s">
         <v>23</v>
@@ -3179,13 +3193,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" t="s">
         <v>111</v>
       </c>
-      <c r="B46" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" t="s">
-        <v>121</v>
+      <c r="C46" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="D46" t="s">
         <v>126</v>
@@ -3209,26 +3223,26 @@
         <v>7</v>
       </c>
       <c r="L46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M46" t="s">
         <v>23</v>
       </c>
       <c r="N46" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O46" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" t="s">
         <v>111</v>
       </c>
-      <c r="B47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="C47" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D47" t="s">
@@ -3253,26 +3267,26 @@
         <v>3</v>
       </c>
       <c r="L47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M47" t="s">
         <v>23</v>
       </c>
       <c r="N47" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O47" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" t="s">
         <v>111</v>
       </c>
-      <c r="B48" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="C48" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D48" t="s">
@@ -3297,27 +3311,27 @@
         <v>9</v>
       </c>
       <c r="L48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M48" t="s">
         <v>23</v>
       </c>
       <c r="N48" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O48" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" t="s">
         <v>111</v>
       </c>
-      <c r="B49" t="s">
-        <v>112</v>
-      </c>
-      <c r="C49" t="s">
-        <v>121</v>
+      <c r="C49" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="D49" t="s">
         <v>133</v>
@@ -3341,26 +3355,26 @@
         <v>9</v>
       </c>
       <c r="L49" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M49" t="s">
         <v>23</v>
       </c>
       <c r="N49" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O49" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" t="s">
         <v>111</v>
       </c>
-      <c r="B50" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="C50" s="3" t="s">
         <v>135</v>
       </c>
       <c r="D50" t="s">
@@ -3385,20 +3399,26 @@
         <v>9</v>
       </c>
       <c r="L50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M50" t="s">
         <v>23</v>
+      </c>
+      <c r="N50" t="s">
+        <v>50</v>
+      </c>
+      <c r="O50" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
         <v>111</v>
       </c>
-      <c r="B51" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="C51" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D51" t="s">
@@ -3423,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M51" t="s">
         <v>23</v>
@@ -3431,16 +3451,16 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" t="s">
         <v>111</v>
       </c>
-      <c r="B52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C52" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" t="s">
         <v>80</v>
-      </c>
-      <c r="E52" t="s">
-        <v>81</v>
       </c>
       <c r="G52" t="s">
         <v>25</v>
@@ -3458,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M52" t="s">
         <v>23</v>
@@ -3466,25 +3486,25 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" t="s">
         <v>111</v>
       </c>
-      <c r="B53" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" t="s">
-        <v>83</v>
+      <c r="C53" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="D53" t="s">
         <v>143</v>
       </c>
       <c r="E53" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53" t="s">
         <v>85</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>86</v>
-      </c>
-      <c r="H53" t="s">
-        <v>87</v>
       </c>
       <c r="I53" t="s">
         <v>21</v>
@@ -3496,36 +3516,36 @@
         <v>0</v>
       </c>
       <c r="L53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M53" t="s">
         <v>23</v>
       </c>
       <c r="N53" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s">
         <v>111</v>
       </c>
-      <c r="B54" t="s">
-        <v>112</v>
-      </c>
-      <c r="C54" t="s">
-        <v>83</v>
+      <c r="C54" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="D54" t="s">
         <v>143</v>
       </c>
       <c r="E54" t="s">
+        <v>87</v>
+      </c>
+      <c r="G54" t="s">
+        <v>85</v>
+      </c>
+      <c r="H54" t="s">
         <v>88</v>
-      </c>
-      <c r="G54" t="s">
-        <v>86</v>
-      </c>
-      <c r="H54" t="s">
-        <v>89</v>
       </c>
       <c r="I54" t="s">
         <v>21</v>
@@ -3537,36 +3557,36 @@
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M54" t="s">
         <v>23</v>
       </c>
       <c r="N54" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" t="s">
         <v>111</v>
       </c>
-      <c r="B55" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" t="s">
-        <v>96</v>
+      <c r="C55" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D55" t="s">
         <v>144</v>
       </c>
       <c r="E55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G55" t="s">
+        <v>85</v>
+      </c>
+      <c r="H55" t="s">
         <v>86</v>
-      </c>
-      <c r="H55" t="s">
-        <v>87</v>
       </c>
       <c r="I55" t="s">
         <v>21</v>
@@ -3578,36 +3598,36 @@
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M55" t="s">
         <v>23</v>
       </c>
       <c r="N55" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" t="s">
         <v>111</v>
       </c>
-      <c r="B56" t="s">
-        <v>112</v>
-      </c>
-      <c r="C56" t="s">
-        <v>96</v>
+      <c r="C56" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D56" t="s">
         <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I56" t="s">
         <v>21</v>
@@ -3619,36 +3639,36 @@
         <v>0</v>
       </c>
       <c r="L56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M56" t="s">
         <v>23</v>
       </c>
       <c r="N56" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" t="s">
         <v>111</v>
       </c>
-      <c r="B57" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" t="s">
-        <v>96</v>
+      <c r="C57" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
       </c>
       <c r="E57" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G57" t="s">
+        <v>85</v>
+      </c>
+      <c r="H57" t="s">
         <v>86</v>
-      </c>
-      <c r="H57" t="s">
-        <v>87</v>
       </c>
       <c r="I57" t="s">
         <v>21</v>
@@ -3660,36 +3680,36 @@
         <v>0</v>
       </c>
       <c r="L57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M57" t="s">
         <v>23</v>
       </c>
       <c r="N57" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" t="s">
         <v>111</v>
       </c>
-      <c r="B58" t="s">
-        <v>112</v>
-      </c>
-      <c r="C58" t="s">
-        <v>96</v>
+      <c r="C58" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
       </c>
       <c r="E58" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G58" t="s">
+        <v>85</v>
+      </c>
+      <c r="H58" t="s">
         <v>86</v>
-      </c>
-      <c r="H58" t="s">
-        <v>87</v>
       </c>
       <c r="I58" t="s">
         <v>21</v>
@@ -3701,36 +3721,36 @@
         <v>0</v>
       </c>
       <c r="L58" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M58" t="s">
         <v>23</v>
       </c>
       <c r="N58" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" t="s">
         <v>111</v>
       </c>
-      <c r="B59" t="s">
-        <v>112</v>
-      </c>
-      <c r="C59" t="s">
-        <v>96</v>
+      <c r="C59" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
       </c>
       <c r="E59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G59" t="s">
+        <v>85</v>
+      </c>
+      <c r="H59" t="s">
         <v>86</v>
-      </c>
-      <c r="H59" t="s">
-        <v>87</v>
       </c>
       <c r="I59" t="s">
         <v>21</v>
@@ -3742,36 +3762,36 @@
         <v>0</v>
       </c>
       <c r="L59" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M59" t="s">
         <v>23</v>
       </c>
       <c r="N59" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" t="s">
         <v>111</v>
       </c>
-      <c r="B60" t="s">
-        <v>112</v>
-      </c>
-      <c r="C60" t="s">
-        <v>96</v>
+      <c r="C60" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
       </c>
       <c r="E60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H60" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s">
         <v>21</v>
@@ -3783,36 +3803,36 @@
         <v>0</v>
       </c>
       <c r="L60" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M60" t="s">
         <v>23</v>
       </c>
       <c r="N60" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>110</v>
+      </c>
+      <c r="B61" t="s">
         <v>111</v>
       </c>
-      <c r="B61" t="s">
-        <v>112</v>
-      </c>
-      <c r="C61" t="s">
-        <v>106</v>
+      <c r="C61" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D61" t="s">
         <v>146</v>
       </c>
       <c r="E61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G61" t="s">
+        <v>85</v>
+      </c>
+      <c r="H61" t="s">
         <v>86</v>
-      </c>
-      <c r="H61" t="s">
-        <v>87</v>
       </c>
       <c r="I61" t="s">
         <v>21</v>
@@ -3824,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M61" t="s">
         <v>23</v>
@@ -3832,25 +3852,25 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>110</v>
+      </c>
+      <c r="B62" t="s">
         <v>111</v>
       </c>
-      <c r="B62" t="s">
-        <v>112</v>
-      </c>
-      <c r="C62" t="s">
-        <v>106</v>
+      <c r="C62" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D62" t="s">
         <v>146</v>
       </c>
       <c r="E62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I62" t="s">
         <v>21</v>
@@ -3862,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M62" t="s">
         <v>23</v>
@@ -3870,25 +3890,25 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>110</v>
+      </c>
+      <c r="B63" t="s">
         <v>111</v>
       </c>
-      <c r="B63" t="s">
-        <v>112</v>
-      </c>
-      <c r="C63" t="s">
-        <v>106</v>
+      <c r="C63" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D63" t="s">
         <v>146</v>
       </c>
       <c r="E63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G63" t="s">
+        <v>85</v>
+      </c>
+      <c r="H63" t="s">
         <v>86</v>
-      </c>
-      <c r="H63" t="s">
-        <v>87</v>
       </c>
       <c r="I63" t="s">
         <v>21</v>
@@ -3900,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M63" t="s">
         <v>23</v>
@@ -3913,7 +3933,7 @@
       <c r="B64" t="s">
         <v>148</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
@@ -3948,11 +3968,11 @@
       <c r="B65" t="s">
         <v>148</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E65" t="s">
         <v>29</v>
@@ -3983,7 +4003,7 @@
       <c r="B66" t="s">
         <v>148</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D66" t="s">
@@ -4018,8 +4038,8 @@
       <c r="B67" t="s">
         <v>148</v>
       </c>
-      <c r="C67" t="s">
-        <v>80</v>
+      <c r="C67" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D67" t="s">
         <v>32</v>
@@ -4053,14 +4073,14 @@
       <c r="B68" t="s">
         <v>148</v>
       </c>
-      <c r="C68" t="s">
-        <v>53</v>
+      <c r="C68" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="D68" t="s">
         <v>153</v>
       </c>
       <c r="E68" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G68" t="s">
         <v>36</v>
@@ -4081,10 +4101,10 @@
         <v>23</v>
       </c>
       <c r="N68" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
@@ -4094,14 +4114,14 @@
       <c r="B69" t="s">
         <v>148</v>
       </c>
-      <c r="C69" t="s">
-        <v>58</v>
+      <c r="C69" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D69" t="s">
         <v>156</v>
       </c>
       <c r="E69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G69" t="s">
         <v>36</v>
@@ -4122,10 +4142,10 @@
         <v>23</v>
       </c>
       <c r="N69" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
@@ -4135,8 +4155,8 @@
       <c r="B70" t="s">
         <v>148</v>
       </c>
-      <c r="C70" t="s">
-        <v>58</v>
+      <c r="C70" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D70" t="s">
         <v>158</v>
@@ -4163,10 +4183,10 @@
         <v>23</v>
       </c>
       <c r="N70" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O70" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
@@ -4176,8 +4196,8 @@
       <c r="B71" t="s">
         <v>148</v>
       </c>
-      <c r="C71" t="s">
-        <v>58</v>
+      <c r="C71" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D71" t="s">
         <v>160</v>
@@ -4204,10 +4224,10 @@
         <v>23</v>
       </c>
       <c r="N71" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O71" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
@@ -4217,7 +4237,7 @@
       <c r="B72" t="s">
         <v>148</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D72" t="s">
@@ -4245,7 +4265,7 @@
         <v>23</v>
       </c>
       <c r="N72" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
@@ -4255,7 +4275,7 @@
       <c r="B73" t="s">
         <v>148</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D73" t="s">
@@ -4283,7 +4303,7 @@
         <v>23</v>
       </c>
       <c r="N73" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
@@ -4293,14 +4313,14 @@
       <c r="B74" t="s">
         <v>148</v>
       </c>
-      <c r="C74" t="s">
-        <v>63</v>
+      <c r="C74" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="D74" t="s">
         <v>164</v>
       </c>
       <c r="E74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G74" t="s">
         <v>36</v>
@@ -4321,10 +4341,10 @@
         <v>23</v>
       </c>
       <c r="N74" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O74" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
@@ -4334,7 +4354,7 @@
       <c r="B75" t="s">
         <v>148</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D75" t="s">
@@ -4362,7 +4382,7 @@
         <v>23</v>
       </c>
       <c r="N75" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
@@ -4372,7 +4392,7 @@
       <c r="B76" t="s">
         <v>148</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D76" t="s">
@@ -4400,7 +4420,7 @@
         <v>23</v>
       </c>
       <c r="N76" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
@@ -4410,14 +4430,14 @@
       <c r="B77" t="s">
         <v>148</v>
       </c>
-      <c r="C77" t="s">
-        <v>49</v>
+      <c r="C77" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D77" t="s">
         <v>169</v>
       </c>
       <c r="E77" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G77" t="s">
         <v>36</v>
@@ -4438,10 +4458,10 @@
         <v>23</v>
       </c>
       <c r="N77" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O77" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
@@ -4451,11 +4471,11 @@
       <c r="B78" t="s">
         <v>148</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E78" t="s">
         <v>80</v>
-      </c>
-      <c r="E78" t="s">
-        <v>81</v>
       </c>
       <c r="G78" t="s">
         <v>36</v>
@@ -4483,7 +4503,7 @@
       <c r="B79" t="s">
         <v>172</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D79" t="s">
@@ -4518,11 +4538,11 @@
       <c r="B80" t="s">
         <v>172</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E80" t="s">
         <v>29</v>
@@ -4553,7 +4573,7 @@
       <c r="B81" t="s">
         <v>172</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
@@ -4588,8 +4608,8 @@
       <c r="B82" t="s">
         <v>172</v>
       </c>
-      <c r="C82" t="s">
-        <v>80</v>
+      <c r="C82" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D82" t="s">
         <v>176</v>
@@ -4623,7 +4643,7 @@
       <c r="B83" t="s">
         <v>172</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D83" t="s">
@@ -4658,14 +4678,14 @@
       <c r="B84" t="s">
         <v>172</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D84" t="s">
         <v>39</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>40</v>
-      </c>
-      <c r="E84" t="s">
-        <v>41</v>
       </c>
       <c r="G84" t="s">
         <v>36</v>
@@ -4686,7 +4706,7 @@
         <v>23</v>
       </c>
       <c r="N84" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
@@ -4696,7 +4716,7 @@
       <c r="B85" t="s">
         <v>172</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D85" t="s">
@@ -4731,7 +4751,7 @@
       <c r="B86" t="s">
         <v>172</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E86" t="s">
@@ -4763,11 +4783,11 @@
       <c r="B87" t="s">
         <v>172</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E87" t="s">
         <v>80</v>
-      </c>
-      <c r="E87" t="s">
-        <v>81</v>
       </c>
       <c r="G87" t="s">
         <v>36</v>
@@ -4795,20 +4815,20 @@
       <c r="B88" t="s">
         <v>172</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D88" t="s">
         <v>83</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>84</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>85</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>86</v>
-      </c>
-      <c r="H88" t="s">
-        <v>87</v>
       </c>
       <c r="I88" t="s">
         <v>21</v>
@@ -4823,7 +4843,7 @@
         <v>23</v>
       </c>
       <c r="N88" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
@@ -4833,20 +4853,20 @@
       <c r="B89" t="s">
         <v>172</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" t="s">
         <v>83</v>
       </c>
-      <c r="D89" t="s">
-        <v>84</v>
-      </c>
       <c r="E89" t="s">
+        <v>87</v>
+      </c>
+      <c r="G89" t="s">
+        <v>85</v>
+      </c>
+      <c r="H89" t="s">
         <v>88</v>
-      </c>
-      <c r="G89" t="s">
-        <v>86</v>
-      </c>
-      <c r="H89" t="s">
-        <v>89</v>
       </c>
       <c r="I89" t="s">
         <v>21</v>
@@ -4861,7 +4881,7 @@
         <v>23</v>
       </c>
       <c r="N89" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
@@ -4871,20 +4891,20 @@
       <c r="B90" t="s">
         <v>172</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D90" t="s">
         <v>90</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>91</v>
       </c>
-      <c r="E90" t="s">
-        <v>92</v>
-      </c>
       <c r="G90" t="s">
+        <v>85</v>
+      </c>
+      <c r="H90" t="s">
         <v>86</v>
-      </c>
-      <c r="H90" t="s">
-        <v>87</v>
       </c>
       <c r="I90" t="s">
         <v>21</v>
@@ -4899,7 +4919,7 @@
         <v>23</v>
       </c>
       <c r="N90" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
@@ -4909,20 +4929,20 @@
       <c r="B91" t="s">
         <v>172</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D91" t="s">
         <v>90</v>
       </c>
-      <c r="D91" t="s">
-        <v>91</v>
-      </c>
       <c r="E91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G91" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I91" t="s">
         <v>21</v>
@@ -4937,7 +4957,7 @@
         <v>23</v>
       </c>
       <c r="N91" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
@@ -4947,20 +4967,20 @@
       <c r="B92" t="s">
         <v>172</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D92" t="s">
         <v>90</v>
       </c>
-      <c r="D92" t="s">
-        <v>91</v>
-      </c>
       <c r="E92" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G92" t="s">
+        <v>85</v>
+      </c>
+      <c r="H92" t="s">
         <v>86</v>
-      </c>
-      <c r="H92" t="s">
-        <v>87</v>
       </c>
       <c r="I92" t="s">
         <v>21</v>
@@ -4975,7 +4995,7 @@
         <v>23</v>
       </c>
       <c r="N92" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
@@ -4985,20 +5005,20 @@
       <c r="B93" t="s">
         <v>172</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D93" t="s">
         <v>90</v>
       </c>
-      <c r="D93" t="s">
-        <v>91</v>
-      </c>
       <c r="E93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G93" t="s">
+        <v>85</v>
+      </c>
+      <c r="H93" t="s">
         <v>86</v>
-      </c>
-      <c r="H93" t="s">
-        <v>87</v>
       </c>
       <c r="I93" t="s">
         <v>21</v>
@@ -5013,7 +5033,7 @@
         <v>23</v>
       </c>
       <c r="N93" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
@@ -5023,20 +5043,20 @@
       <c r="B94" t="s">
         <v>172</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D94" t="s">
         <v>96</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>97</v>
       </c>
-      <c r="E94" t="s">
-        <v>98</v>
-      </c>
       <c r="G94" t="s">
+        <v>85</v>
+      </c>
+      <c r="H94" t="s">
         <v>86</v>
-      </c>
-      <c r="H94" t="s">
-        <v>87</v>
       </c>
       <c r="I94" t="s">
         <v>21</v>
@@ -5051,7 +5071,7 @@
         <v>23</v>
       </c>
       <c r="N94" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
@@ -5061,20 +5081,20 @@
       <c r="B95" t="s">
         <v>172</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D95" t="s">
         <v>96</v>
       </c>
-      <c r="D95" t="s">
-        <v>97</v>
-      </c>
       <c r="E95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G95" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H95" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I95" t="s">
         <v>21</v>
@@ -5089,7 +5109,7 @@
         <v>23</v>
       </c>
       <c r="N95" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
@@ -5099,20 +5119,20 @@
       <c r="B96" t="s">
         <v>172</v>
       </c>
-      <c r="C96" t="s">
-        <v>96</v>
+      <c r="C96" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D96" t="s">
+        <v>99</v>
+      </c>
+      <c r="E96" t="s">
         <v>100</v>
       </c>
-      <c r="E96" t="s">
-        <v>101</v>
-      </c>
       <c r="G96" t="s">
+        <v>85</v>
+      </c>
+      <c r="H96" t="s">
         <v>86</v>
-      </c>
-      <c r="H96" t="s">
-        <v>87</v>
       </c>
       <c r="I96" t="s">
         <v>21</v>
@@ -5127,7 +5147,7 @@
         <v>23</v>
       </c>
       <c r="N96" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
@@ -5137,20 +5157,20 @@
       <c r="B97" t="s">
         <v>172</v>
       </c>
-      <c r="C97" t="s">
-        <v>96</v>
+      <c r="C97" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G97" t="s">
+        <v>85</v>
+      </c>
+      <c r="H97" t="s">
         <v>86</v>
-      </c>
-      <c r="H97" t="s">
-        <v>87</v>
       </c>
       <c r="I97" t="s">
         <v>21</v>
@@ -5165,7 +5185,7 @@
         <v>23</v>
       </c>
       <c r="N97" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
@@ -5175,20 +5195,20 @@
       <c r="B98" t="s">
         <v>172</v>
       </c>
-      <c r="C98" t="s">
-        <v>96</v>
+      <c r="C98" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D98" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G98" t="s">
+        <v>85</v>
+      </c>
+      <c r="H98" t="s">
         <v>86</v>
-      </c>
-      <c r="H98" t="s">
-        <v>87</v>
       </c>
       <c r="I98" t="s">
         <v>21</v>
@@ -5203,7 +5223,7 @@
         <v>23</v>
       </c>
       <c r="N98" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
@@ -5213,20 +5233,20 @@
       <c r="B99" t="s">
         <v>172</v>
       </c>
-      <c r="C99" t="s">
-        <v>96</v>
+      <c r="C99" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G99" t="s">
+        <v>85</v>
+      </c>
+      <c r="H99" t="s">
         <v>86</v>
-      </c>
-      <c r="H99" t="s">
-        <v>87</v>
       </c>
       <c r="I99" t="s">
         <v>21</v>
@@ -5241,7 +5261,7 @@
         <v>23</v>
       </c>
       <c r="N99" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
@@ -5251,20 +5271,20 @@
       <c r="B100" t="s">
         <v>172</v>
       </c>
-      <c r="C100" t="s">
-        <v>96</v>
+      <c r="C100" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D100" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E100" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G100" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H100" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I100" t="s">
         <v>21</v>
@@ -5279,7 +5299,7 @@
         <v>23</v>
       </c>
       <c r="N100" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
@@ -5287,9 +5307,9 @@
         <v>186</v>
       </c>
       <c r="B101" t="s">
-        <v>58</v>
-      </c>
-      <c r="C101" t="s">
+        <v>57</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D101" t="s">
@@ -5322,13 +5342,13 @@
         <v>186</v>
       </c>
       <c r="B102" t="s">
-        <v>58</v>
-      </c>
-      <c r="C102" t="s">
+        <v>57</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D102" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E102" t="s">
         <v>29</v>
@@ -5357,9 +5377,9 @@
         <v>186</v>
       </c>
       <c r="B103" t="s">
-        <v>58</v>
-      </c>
-      <c r="C103" t="s">
+        <v>57</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D103" t="s">
@@ -5392,10 +5412,10 @@
         <v>186</v>
       </c>
       <c r="B104" t="s">
-        <v>58</v>
-      </c>
-      <c r="C104" t="s">
-        <v>80</v>
+        <v>57</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D104" t="s">
         <v>176</v>
@@ -5427,16 +5447,16 @@
         <v>186</v>
       </c>
       <c r="B105" t="s">
-        <v>58</v>
-      </c>
-      <c r="C105" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D105" t="s">
         <v>190</v>
       </c>
       <c r="E105" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G105" t="s">
         <v>36</v>
@@ -5457,10 +5477,10 @@
         <v>23</v>
       </c>
       <c r="N105" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O105" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
@@ -5468,13 +5488,13 @@
         <v>186</v>
       </c>
       <c r="B106" t="s">
-        <v>58</v>
-      </c>
-      <c r="C106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E106" t="s">
         <v>80</v>
-      </c>
-      <c r="E106" t="s">
-        <v>81</v>
       </c>
       <c r="G106" t="s">
         <v>36</v>
@@ -5502,7 +5522,7 @@
       <c r="B107" t="s">
         <v>194</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D107" t="s">
@@ -5540,11 +5560,11 @@
       <c r="B108" t="s">
         <v>194</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D108" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E108" t="s">
         <v>29</v>
@@ -5578,7 +5598,7 @@
       <c r="B109" t="s">
         <v>194</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D109" t="s">
@@ -5616,8 +5636,8 @@
       <c r="B110" t="s">
         <v>194</v>
       </c>
-      <c r="C110" t="s">
-        <v>80</v>
+      <c r="C110" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D110" t="s">
         <v>32</v>
@@ -5654,8 +5674,8 @@
       <c r="B111" t="s">
         <v>194</v>
       </c>
-      <c r="C111" t="s">
-        <v>106</v>
+      <c r="C111" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D111" t="s">
         <v>200</v>
@@ -5692,11 +5712,11 @@
       <c r="B112" t="s">
         <v>194</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E112" t="s">
         <v>80</v>
-      </c>
-      <c r="E112" t="s">
-        <v>81</v>
       </c>
       <c r="G112" t="s">
         <v>25</v>
@@ -5727,20 +5747,20 @@
       <c r="B113" t="s">
         <v>194</v>
       </c>
-      <c r="C113" t="s">
-        <v>106</v>
+      <c r="C113" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D113" t="s">
         <v>204</v>
       </c>
       <c r="E113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G113" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H113" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I113" t="s">
         <v>21</v>
@@ -5765,20 +5785,20 @@
       <c r="B114" t="s">
         <v>194</v>
       </c>
-      <c r="C114" t="s">
-        <v>106</v>
+      <c r="C114" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D114" t="s">
         <v>204</v>
       </c>
       <c r="E114" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G114" t="s">
+        <v>85</v>
+      </c>
+      <c r="H114" t="s">
         <v>86</v>
-      </c>
-      <c r="H114" t="s">
-        <v>87</v>
       </c>
       <c r="I114" t="s">
         <v>21</v>
@@ -5803,20 +5823,20 @@
       <c r="B115" t="s">
         <v>194</v>
       </c>
-      <c r="C115" t="s">
-        <v>106</v>
+      <c r="C115" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D115" t="s">
         <v>204</v>
       </c>
       <c r="E115" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G115" t="s">
+        <v>85</v>
+      </c>
+      <c r="H115" t="s">
         <v>86</v>
-      </c>
-      <c r="H115" t="s">
-        <v>87</v>
       </c>
       <c r="I115" t="s">
         <v>21</v>
@@ -5841,7 +5861,7 @@
       <c r="B116" t="s">
         <v>206</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D116" t="s">
@@ -5879,8 +5899,8 @@
       <c r="B117" t="s">
         <v>206</v>
       </c>
-      <c r="C117" t="s">
-        <v>80</v>
+      <c r="C117" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D117" t="s">
         <v>32</v>
@@ -5917,7 +5937,7 @@
       <c r="B118" t="s">
         <v>206</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D118" t="s">
@@ -5955,8 +5975,8 @@
       <c r="B119" t="s">
         <v>206</v>
       </c>
-      <c r="C119" t="s">
-        <v>64</v>
+      <c r="C119" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D119" t="s">
         <v>212</v>
@@ -5989,10 +6009,10 @@
         <v>23</v>
       </c>
       <c r="N119" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O119" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
@@ -6002,14 +6022,14 @@
       <c r="B120" t="s">
         <v>206</v>
       </c>
-      <c r="C120" t="s">
-        <v>64</v>
+      <c r="C120" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D120" t="s">
         <v>216</v>
       </c>
       <c r="E120" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F120" t="s">
         <v>214</v>
@@ -6036,10 +6056,10 @@
         <v>23</v>
       </c>
       <c r="N120" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O120" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
@@ -6049,8 +6069,8 @@
       <c r="B121" t="s">
         <v>206</v>
       </c>
-      <c r="C121" t="s">
-        <v>64</v>
+      <c r="C121" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D121" t="s">
         <v>218</v>
@@ -6083,10 +6103,10 @@
         <v>23</v>
       </c>
       <c r="N121" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O121" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
@@ -6096,8 +6116,8 @@
       <c r="B122" t="s">
         <v>206</v>
       </c>
-      <c r="C122" t="s">
-        <v>64</v>
+      <c r="C122" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D122" t="s">
         <v>221</v>
@@ -6130,10 +6150,10 @@
         <v>23</v>
       </c>
       <c r="N122" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O122" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
@@ -6143,8 +6163,8 @@
       <c r="B123" t="s">
         <v>206</v>
       </c>
-      <c r="C123" t="s">
-        <v>64</v>
+      <c r="C123" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D123" t="s">
         <v>224</v>
@@ -6177,10 +6197,10 @@
         <v>23</v>
       </c>
       <c r="N123" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O123" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
@@ -6190,8 +6210,8 @@
       <c r="B124" t="s">
         <v>206</v>
       </c>
-      <c r="C124" t="s">
-        <v>64</v>
+      <c r="C124" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D124" t="s">
         <v>227</v>
@@ -6224,10 +6244,10 @@
         <v>23</v>
       </c>
       <c r="N124" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O124" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
@@ -6237,8 +6257,8 @@
       <c r="B125" t="s">
         <v>206</v>
       </c>
-      <c r="C125" t="s">
-        <v>64</v>
+      <c r="C125" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D125" t="s">
         <v>230</v>
@@ -6271,10 +6291,10 @@
         <v>23</v>
       </c>
       <c r="N125" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O125" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
@@ -6284,8 +6304,8 @@
       <c r="B126" t="s">
         <v>206</v>
       </c>
-      <c r="C126" t="s">
-        <v>64</v>
+      <c r="C126" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D126" t="s">
         <v>233</v>
@@ -6318,10 +6338,10 @@
         <v>23</v>
       </c>
       <c r="N126" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O126" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
@@ -6331,8 +6351,8 @@
       <c r="B127" t="s">
         <v>206</v>
       </c>
-      <c r="C127" t="s">
-        <v>64</v>
+      <c r="C127" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D127" t="s">
         <v>236</v>
@@ -6365,10 +6385,10 @@
         <v>23</v>
       </c>
       <c r="N127" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O127" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
@@ -6378,8 +6398,8 @@
       <c r="B128" t="s">
         <v>206</v>
       </c>
-      <c r="C128" t="s">
-        <v>64</v>
+      <c r="C128" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D128" t="s">
         <v>239</v>
@@ -6412,10 +6432,10 @@
         <v>23</v>
       </c>
       <c r="N128" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O128" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
@@ -6425,8 +6445,8 @@
       <c r="B129" t="s">
         <v>206</v>
       </c>
-      <c r="C129" t="s">
-        <v>64</v>
+      <c r="C129" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D129" t="s">
         <v>242</v>
@@ -6459,10 +6479,10 @@
         <v>23</v>
       </c>
       <c r="N129" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O129" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
@@ -6472,11 +6492,11 @@
       <c r="B130" t="s">
         <v>206</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E130" t="s">
         <v>80</v>
-      </c>
-      <c r="E130" t="s">
-        <v>81</v>
       </c>
       <c r="G130" t="s">
         <v>25</v>
@@ -6507,7 +6527,7 @@
       <c r="B131" t="s">
         <v>247</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D131" t="s">
@@ -6545,7 +6565,7 @@
       <c r="B132" t="s">
         <v>247</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D132" t="s">
@@ -6583,8 +6603,8 @@
       <c r="B133" t="s">
         <v>247</v>
       </c>
-      <c r="C133" t="s">
-        <v>80</v>
+      <c r="C133" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D133" t="s">
         <v>32</v>
@@ -6621,8 +6641,8 @@
       <c r="B134" t="s">
         <v>247</v>
       </c>
-      <c r="C134" t="s">
-        <v>64</v>
+      <c r="C134" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D134" t="s">
         <v>212</v>
@@ -6655,10 +6675,10 @@
         <v>23</v>
       </c>
       <c r="N134" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O134" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
@@ -6668,14 +6688,14 @@
       <c r="B135" t="s">
         <v>247</v>
       </c>
-      <c r="C135" t="s">
-        <v>64</v>
+      <c r="C135" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D135" t="s">
         <v>216</v>
       </c>
       <c r="E135" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F135" t="s">
         <v>214</v>
@@ -6702,10 +6722,10 @@
         <v>23</v>
       </c>
       <c r="N135" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O135" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
@@ -6715,8 +6735,8 @@
       <c r="B136" t="s">
         <v>247</v>
       </c>
-      <c r="C136" t="s">
-        <v>64</v>
+      <c r="C136" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D136" t="s">
         <v>218</v>
@@ -6749,10 +6769,10 @@
         <v>23</v>
       </c>
       <c r="N136" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O136" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
@@ -6762,8 +6782,8 @@
       <c r="B137" t="s">
         <v>247</v>
       </c>
-      <c r="C137" t="s">
-        <v>64</v>
+      <c r="C137" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D137" t="s">
         <v>221</v>
@@ -6796,10 +6816,10 @@
         <v>23</v>
       </c>
       <c r="N137" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O137" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
@@ -6809,8 +6829,8 @@
       <c r="B138" t="s">
         <v>247</v>
       </c>
-      <c r="C138" t="s">
-        <v>64</v>
+      <c r="C138" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D138" t="s">
         <v>224</v>
@@ -6843,10 +6863,10 @@
         <v>23</v>
       </c>
       <c r="N138" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O138" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
@@ -6856,8 +6876,8 @@
       <c r="B139" t="s">
         <v>247</v>
       </c>
-      <c r="C139" t="s">
-        <v>64</v>
+      <c r="C139" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D139" t="s">
         <v>227</v>
@@ -6890,10 +6910,10 @@
         <v>23</v>
       </c>
       <c r="N139" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O139" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
@@ -6903,8 +6923,8 @@
       <c r="B140" t="s">
         <v>247</v>
       </c>
-      <c r="C140" t="s">
-        <v>64</v>
+      <c r="C140" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D140" t="s">
         <v>230</v>
@@ -6937,10 +6957,10 @@
         <v>23</v>
       </c>
       <c r="N140" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O140" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
@@ -6950,8 +6970,8 @@
       <c r="B141" t="s">
         <v>247</v>
       </c>
-      <c r="C141" t="s">
-        <v>64</v>
+      <c r="C141" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D141" t="s">
         <v>233</v>
@@ -6984,10 +7004,10 @@
         <v>23</v>
       </c>
       <c r="N141" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O141" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.3">
@@ -6997,8 +7017,8 @@
       <c r="B142" t="s">
         <v>247</v>
       </c>
-      <c r="C142" t="s">
-        <v>64</v>
+      <c r="C142" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D142" t="s">
         <v>236</v>
@@ -7031,10 +7051,10 @@
         <v>23</v>
       </c>
       <c r="N142" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O142" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
@@ -7044,8 +7064,8 @@
       <c r="B143" t="s">
         <v>247</v>
       </c>
-      <c r="C143" t="s">
-        <v>64</v>
+      <c r="C143" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D143" t="s">
         <v>239</v>
@@ -7078,10 +7098,10 @@
         <v>23</v>
       </c>
       <c r="N143" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O143" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
@@ -7091,8 +7111,8 @@
       <c r="B144" t="s">
         <v>247</v>
       </c>
-      <c r="C144" t="s">
-        <v>64</v>
+      <c r="C144" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D144" t="s">
         <v>242</v>
@@ -7125,10 +7145,10 @@
         <v>23</v>
       </c>
       <c r="N144" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O144" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.3">
@@ -7138,8 +7158,11 @@
       <c r="B145" t="s">
         <v>247</v>
       </c>
+      <c r="C145" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="E145" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G145" t="s">
         <v>25</v>
@@ -7148,7 +7171,7 @@
         <v>21</v>
       </c>
       <c r="I145" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J145">
         <v>4190</v>
@@ -7170,7 +7193,7 @@
       <c r="B146" t="s">
         <v>264</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
@@ -7208,14 +7231,14 @@
       <c r="B147" t="s">
         <v>264</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D147" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E147" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G147" t="s">
         <v>19</v>
@@ -7246,8 +7269,8 @@
       <c r="B148" t="s">
         <v>264</v>
       </c>
-      <c r="C148" t="s">
-        <v>80</v>
+      <c r="C148" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D148" t="s">
         <v>32</v>
@@ -7284,7 +7307,7 @@
       <c r="B149" t="s">
         <v>264</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D149" t="s">
@@ -7322,8 +7345,8 @@
       <c r="B150" t="s">
         <v>264</v>
       </c>
-      <c r="C150" t="s">
-        <v>64</v>
+      <c r="C150" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D150" t="s">
         <v>212</v>
@@ -7356,10 +7379,10 @@
         <v>23</v>
       </c>
       <c r="N150" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O150" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
@@ -7369,14 +7392,14 @@
       <c r="B151" t="s">
         <v>264</v>
       </c>
-      <c r="C151" t="s">
-        <v>64</v>
+      <c r="C151" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D151" t="s">
         <v>216</v>
       </c>
       <c r="E151" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F151" t="s">
         <v>214</v>
@@ -7403,10 +7426,10 @@
         <v>23</v>
       </c>
       <c r="N151" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O151" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.3">
@@ -7416,8 +7439,8 @@
       <c r="B152" t="s">
         <v>264</v>
       </c>
-      <c r="C152" t="s">
-        <v>64</v>
+      <c r="C152" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D152" t="s">
         <v>218</v>
@@ -7450,10 +7473,10 @@
         <v>23</v>
       </c>
       <c r="N152" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O152" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.3">
@@ -7463,8 +7486,8 @@
       <c r="B153" t="s">
         <v>264</v>
       </c>
-      <c r="C153" t="s">
-        <v>64</v>
+      <c r="C153" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D153" t="s">
         <v>221</v>
@@ -7497,10 +7520,10 @@
         <v>23</v>
       </c>
       <c r="N153" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O153" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.3">
@@ -7510,8 +7533,8 @@
       <c r="B154" t="s">
         <v>264</v>
       </c>
-      <c r="C154" t="s">
-        <v>64</v>
+      <c r="C154" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D154" t="s">
         <v>224</v>
@@ -7544,10 +7567,10 @@
         <v>23</v>
       </c>
       <c r="N154" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O154" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.3">
@@ -7557,8 +7580,8 @@
       <c r="B155" t="s">
         <v>264</v>
       </c>
-      <c r="C155" t="s">
-        <v>64</v>
+      <c r="C155" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D155" t="s">
         <v>227</v>
@@ -7591,10 +7614,10 @@
         <v>23</v>
       </c>
       <c r="N155" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O155" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.3">
@@ -7604,8 +7627,8 @@
       <c r="B156" t="s">
         <v>264</v>
       </c>
-      <c r="C156" t="s">
-        <v>64</v>
+      <c r="C156" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D156" t="s">
         <v>230</v>
@@ -7638,10 +7661,10 @@
         <v>23</v>
       </c>
       <c r="N156" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O156" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.3">
@@ -7651,8 +7674,8 @@
       <c r="B157" t="s">
         <v>264</v>
       </c>
-      <c r="C157" t="s">
-        <v>64</v>
+      <c r="C157" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D157" t="s">
         <v>233</v>
@@ -7685,10 +7708,10 @@
         <v>23</v>
       </c>
       <c r="N157" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O157" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
@@ -7698,8 +7721,8 @@
       <c r="B158" t="s">
         <v>264</v>
       </c>
-      <c r="C158" t="s">
-        <v>64</v>
+      <c r="C158" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D158" t="s">
         <v>236</v>
@@ -7732,10 +7755,10 @@
         <v>23</v>
       </c>
       <c r="N158" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O158" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
@@ -7745,8 +7768,8 @@
       <c r="B159" t="s">
         <v>264</v>
       </c>
-      <c r="C159" t="s">
-        <v>64</v>
+      <c r="C159" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D159" t="s">
         <v>239</v>
@@ -7779,10 +7802,10 @@
         <v>23</v>
       </c>
       <c r="N159" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O159" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
@@ -7792,8 +7815,8 @@
       <c r="B160" t="s">
         <v>264</v>
       </c>
-      <c r="C160" t="s">
-        <v>64</v>
+      <c r="C160" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D160" t="s">
         <v>242</v>
@@ -7826,10 +7849,10 @@
         <v>23</v>
       </c>
       <c r="N160" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O160" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.3">
@@ -7839,11 +7862,11 @@
       <c r="B161" t="s">
         <v>264</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E161" t="s">
         <v>80</v>
-      </c>
-      <c r="E161" t="s">
-        <v>81</v>
       </c>
       <c r="G161" t="s">
         <v>25</v>
@@ -7874,7 +7897,7 @@
       <c r="B162" t="s">
         <v>283</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C162" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D162" t="s">
@@ -7912,14 +7935,14 @@
       <c r="B163" t="s">
         <v>283</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C163" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D163" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E163" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G163" t="s">
         <v>19</v>
@@ -7950,8 +7973,8 @@
       <c r="B164" t="s">
         <v>283</v>
       </c>
-      <c r="C164" t="s">
-        <v>80</v>
+      <c r="C164" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D164" t="s">
         <v>32</v>
@@ -7988,7 +8011,7 @@
       <c r="B165" t="s">
         <v>283</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D165" t="s">
@@ -8026,8 +8049,8 @@
       <c r="B166" t="s">
         <v>283</v>
       </c>
-      <c r="C166" t="s">
-        <v>64</v>
+      <c r="C166" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D166" t="s">
         <v>212</v>
@@ -8060,10 +8083,10 @@
         <v>23</v>
       </c>
       <c r="N166" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O166" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
@@ -8073,14 +8096,14 @@
       <c r="B167" t="s">
         <v>283</v>
       </c>
-      <c r="C167" t="s">
-        <v>64</v>
+      <c r="C167" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D167" t="s">
         <v>216</v>
       </c>
       <c r="E167" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F167" t="s">
         <v>214</v>
@@ -8107,10 +8130,10 @@
         <v>23</v>
       </c>
       <c r="N167" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O167" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.3">
@@ -8120,8 +8143,8 @@
       <c r="B168" t="s">
         <v>283</v>
       </c>
-      <c r="C168" t="s">
-        <v>64</v>
+      <c r="C168" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D168" t="s">
         <v>218</v>
@@ -8154,10 +8177,10 @@
         <v>23</v>
       </c>
       <c r="N168" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O168" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.3">
@@ -8167,8 +8190,8 @@
       <c r="B169" t="s">
         <v>283</v>
       </c>
-      <c r="C169" t="s">
-        <v>64</v>
+      <c r="C169" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D169" t="s">
         <v>221</v>
@@ -8201,10 +8224,10 @@
         <v>290</v>
       </c>
       <c r="N169" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O169" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.3">
@@ -8214,8 +8237,8 @@
       <c r="B170" t="s">
         <v>283</v>
       </c>
-      <c r="C170" t="s">
-        <v>64</v>
+      <c r="C170" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D170" t="s">
         <v>224</v>
@@ -8248,10 +8271,10 @@
         <v>23</v>
       </c>
       <c r="N170" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O170" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.3">
@@ -8261,8 +8284,8 @@
       <c r="B171" t="s">
         <v>283</v>
       </c>
-      <c r="C171" t="s">
-        <v>64</v>
+      <c r="C171" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D171" t="s">
         <v>227</v>
@@ -8295,10 +8318,10 @@
         <v>23</v>
       </c>
       <c r="N171" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O171" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.3">
@@ -8308,8 +8331,8 @@
       <c r="B172" t="s">
         <v>283</v>
       </c>
-      <c r="C172" t="s">
-        <v>64</v>
+      <c r="C172" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D172" t="s">
         <v>230</v>
@@ -8342,10 +8365,10 @@
         <v>23</v>
       </c>
       <c r="N172" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O172" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.3">
@@ -8355,8 +8378,8 @@
       <c r="B173" t="s">
         <v>283</v>
       </c>
-      <c r="C173" t="s">
-        <v>64</v>
+      <c r="C173" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D173" t="s">
         <v>233</v>
@@ -8389,10 +8412,10 @@
         <v>23</v>
       </c>
       <c r="N173" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O173" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.3">
@@ -8402,8 +8425,8 @@
       <c r="B174" t="s">
         <v>283</v>
       </c>
-      <c r="C174" t="s">
-        <v>64</v>
+      <c r="C174" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D174" t="s">
         <v>236</v>
@@ -8436,10 +8459,10 @@
         <v>290</v>
       </c>
       <c r="N174" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O174" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.3">
@@ -8449,8 +8472,8 @@
       <c r="B175" t="s">
         <v>283</v>
       </c>
-      <c r="C175" t="s">
-        <v>64</v>
+      <c r="C175" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D175" t="s">
         <v>239</v>
@@ -8483,10 +8506,10 @@
         <v>23</v>
       </c>
       <c r="N175" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O175" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.3">
@@ -8496,8 +8519,8 @@
       <c r="B176" t="s">
         <v>283</v>
       </c>
-      <c r="C176" t="s">
-        <v>64</v>
+      <c r="C176" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D176" t="s">
         <v>242</v>
@@ -8530,10 +8553,10 @@
         <v>23</v>
       </c>
       <c r="N176" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O176" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.3">
@@ -8543,11 +8566,11 @@
       <c r="B177" t="s">
         <v>283</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C177" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E177" t="s">
         <v>80</v>
-      </c>
-      <c r="E177" t="s">
-        <v>81</v>
       </c>
       <c r="G177" t="s">
         <v>25</v>
@@ -8578,7 +8601,7 @@
       <c r="B178" t="s">
         <v>301</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C178" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D178" t="s">
@@ -8616,8 +8639,8 @@
       <c r="B179" t="s">
         <v>301</v>
       </c>
-      <c r="C179" t="s">
-        <v>80</v>
+      <c r="C179" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D179" t="s">
         <v>32</v>
@@ -8654,7 +8677,7 @@
       <c r="B180" t="s">
         <v>301</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D180" t="s">
@@ -8692,8 +8715,8 @@
       <c r="B181" t="s">
         <v>301</v>
       </c>
-      <c r="C181" t="s">
-        <v>64</v>
+      <c r="C181" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D181" t="s">
         <v>212</v>
@@ -8726,10 +8749,10 @@
         <v>23</v>
       </c>
       <c r="N181" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O181" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.3">
@@ -8739,14 +8762,14 @@
       <c r="B182" t="s">
         <v>301</v>
       </c>
-      <c r="C182" t="s">
-        <v>64</v>
+      <c r="C182" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D182" t="s">
         <v>216</v>
       </c>
       <c r="E182" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F182" t="s">
         <v>214</v>
@@ -8773,10 +8796,10 @@
         <v>23</v>
       </c>
       <c r="N182" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O182" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.3">
@@ -8786,8 +8809,8 @@
       <c r="B183" t="s">
         <v>301</v>
       </c>
-      <c r="C183" t="s">
-        <v>64</v>
+      <c r="C183" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D183" t="s">
         <v>218</v>
@@ -8820,10 +8843,10 @@
         <v>23</v>
       </c>
       <c r="N183" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O183" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.3">
@@ -8833,8 +8856,8 @@
       <c r="B184" t="s">
         <v>301</v>
       </c>
-      <c r="C184" t="s">
-        <v>64</v>
+      <c r="C184" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D184" t="s">
         <v>221</v>
@@ -8867,10 +8890,10 @@
         <v>23</v>
       </c>
       <c r="N184" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O184" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.3">
@@ -8880,8 +8903,8 @@
       <c r="B185" t="s">
         <v>301</v>
       </c>
-      <c r="C185" t="s">
-        <v>64</v>
+      <c r="C185" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D185" t="s">
         <v>224</v>
@@ -8914,10 +8937,10 @@
         <v>23</v>
       </c>
       <c r="N185" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O185" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.3">
@@ -8927,8 +8950,8 @@
       <c r="B186" t="s">
         <v>301</v>
       </c>
-      <c r="C186" t="s">
-        <v>64</v>
+      <c r="C186" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D186" t="s">
         <v>227</v>
@@ -8961,10 +8984,10 @@
         <v>23</v>
       </c>
       <c r="N186" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O186" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
@@ -8974,8 +8997,8 @@
       <c r="B187" t="s">
         <v>301</v>
       </c>
-      <c r="C187" t="s">
-        <v>64</v>
+      <c r="C187" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D187" t="s">
         <v>230</v>
@@ -9008,10 +9031,10 @@
         <v>23</v>
       </c>
       <c r="N187" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O187" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
@@ -9021,8 +9044,8 @@
       <c r="B188" t="s">
         <v>301</v>
       </c>
-      <c r="C188" t="s">
-        <v>64</v>
+      <c r="C188" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D188" t="s">
         <v>233</v>
@@ -9055,10 +9078,10 @@
         <v>23</v>
       </c>
       <c r="N188" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O188" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.3">
@@ -9068,8 +9091,8 @@
       <c r="B189" t="s">
         <v>301</v>
       </c>
-      <c r="C189" t="s">
-        <v>64</v>
+      <c r="C189" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D189" t="s">
         <v>236</v>
@@ -9102,10 +9125,10 @@
         <v>23</v>
       </c>
       <c r="N189" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O189" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.3">
@@ -9115,8 +9138,8 @@
       <c r="B190" t="s">
         <v>301</v>
       </c>
-      <c r="C190" t="s">
-        <v>64</v>
+      <c r="C190" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D190" t="s">
         <v>239</v>
@@ -9149,10 +9172,10 @@
         <v>23</v>
       </c>
       <c r="N190" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O190" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.3">
@@ -9162,8 +9185,8 @@
       <c r="B191" t="s">
         <v>301</v>
       </c>
-      <c r="C191" t="s">
-        <v>64</v>
+      <c r="C191" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D191" t="s">
         <v>242</v>
@@ -9196,10 +9219,10 @@
         <v>23</v>
       </c>
       <c r="N191" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O191" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.3">
@@ -9209,11 +9232,11 @@
       <c r="B192" t="s">
         <v>301</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C192" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E192" t="s">
         <v>80</v>
-      </c>
-      <c r="E192" t="s">
-        <v>81</v>
       </c>
       <c r="G192" t="s">
         <v>25</v>
